--- a/zapata_Asientos/Tensiones carga_rectangular_elasticos.xlsx
+++ b/zapata_Asientos/Tensiones carga_rectangular_elasticos.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Documentos\Desarrollo\Python\CalculoPilotes\zapata_Asientos\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2D84ADB-BB61-4B2D-8FD0-BBCF5193AC13}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0E505DA9-576B-4D39-9B05-847DD97E676F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -126,7 +126,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="44">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="43">
   <si>
     <t>Datos</t>
   </si>
@@ -392,9 +392,6 @@
       </rPr>
       <t>[cm]</t>
     </r>
-  </si>
-  <si>
-    <t>Selección del tipo de asientos a calcular</t>
   </si>
   <si>
     <t>Elástico</t>
@@ -1141,7 +1138,7 @@
   <sheetData>
     <row r="2" spans="1:4" ht="19.5">
       <c r="A2" s="23" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="3" spans="1:4" ht="15.75">
@@ -1233,7 +1230,7 @@
         <v>7</v>
       </c>
       <c r="B14" s="8">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="C14" s="10" t="s">
         <v>2</v>
@@ -1248,7 +1245,7 @@
       </c>
       <c r="B15" s="9">
         <f>SUM(N40:N104)</f>
-        <v>1.6039916575914719</v>
+        <v>2.0722981225799582</v>
       </c>
       <c r="C15" s="10" t="s">
         <v>5</v>
@@ -1294,21 +1291,14 @@
     </row>
     <row r="27" spans="1:12">
       <c r="A27" s="6"/>
-      <c r="L27" t="s">
-        <v>38</v>
-      </c>
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="6"/>
-      <c r="L28" s="17">
-        <v>1</v>
-      </c>
+      <c r="L28" s="17"/>
     </row>
     <row r="29" spans="1:12">
       <c r="A29" s="6"/>
-      <c r="L29" s="17">
-        <v>2</v>
-      </c>
+      <c r="L29" s="17"/>
     </row>
     <row r="30" spans="1:12">
       <c r="A30" s="6"/>
@@ -1349,11 +1339,11 @@
       <c r="A37" s="6"/>
       <c r="C37" s="2"/>
       <c r="J37" s="30" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="K37" s="31"/>
       <c r="L37" s="26" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="M37" s="18" t="s">
         <v>22</v>
@@ -1377,7 +1367,7 @@
         <v>29</v>
       </c>
       <c r="M38" s="18" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="N38" s="18" t="s">
         <v>22</v>
@@ -1397,7 +1387,7 @@
         <v>16</v>
       </c>
       <c r="E39" s="11" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="F39" s="11" t="s">
         <v>17</v>
@@ -1464,22 +1454,22 @@
       </c>
       <c r="J40" s="4">
         <f>G40*$B$14</f>
-        <v>64.95185509805934</v>
+        <v>62.453706825057054</v>
       </c>
       <c r="K40" s="4">
         <f t="shared" ref="K40:K71" si="0">4*J40</f>
-        <v>259.80742039223736</v>
+        <v>249.81482730022822</v>
       </c>
       <c r="L40" s="4">
         <v>23000</v>
       </c>
       <c r="M40" s="3">
-        <f>100*$B$12*K40/L40</f>
-        <v>0.11295974799662495</v>
+        <f t="shared" ref="M40:M71" si="1">100*$B$12*K40/L40</f>
+        <v>0.10861514230444705</v>
       </c>
       <c r="N40" s="3">
         <f>M40</f>
-        <v>0.11295974799662495</v>
+        <v>0.10861514230444705</v>
       </c>
     </row>
     <row r="41" spans="1:14">
@@ -1488,27 +1478,27 @@
         <v>0.2</v>
       </c>
       <c r="B41" s="13">
-        <f t="shared" ref="B41:B76" si="1">$B$10/A41</f>
+        <f t="shared" ref="B41:B76" si="2">$B$10/A41</f>
         <v>5</v>
       </c>
       <c r="C41" s="4">
-        <f t="shared" ref="C41:C76" si="2">$B$9/A41</f>
+        <f t="shared" ref="C41:C76" si="3">$B$9/A41</f>
         <v>5</v>
       </c>
       <c r="D41" s="3">
-        <f t="shared" ref="D41:D76" si="3">2*C41*B41*SQRT(B41^2+C41^2+1)*(B41^2+C41^2+2)/((C41^2+B41^2+B41^2*C41^2+1)*(C41^2+B41^2+1))</f>
+        <f t="shared" ref="D41:D76" si="4">2*C41*B41*SQRT(B41^2+C41^2+1)*(B41^2+C41^2+2)/((C41^2+B41^2+B41^2*C41^2+1)*(C41^2+B41^2+1))</f>
         <v>0.53856926308769604</v>
       </c>
       <c r="E41" s="14">
-        <f t="shared" ref="E41:E76" si="4">((2*B41*C41*SQRT(B41^2+C41^2+1)/(B41^2+C41^2-C41^2 *B41^2+1)))</f>
+        <f t="shared" ref="E41:E76" si="5">((2*B41*C41*SQRT(B41^2+C41^2+1)/(B41^2+C41^2-C41^2 *B41^2+1)))</f>
         <v>-0.62207564708561414</v>
       </c>
       <c r="F41" s="4">
-        <f t="shared" ref="F41:F76" si="5">IF(E41&lt;0,ATAN(E41)+PI(),ATAN(E41))</f>
+        <f t="shared" ref="F41:F76" si="6">IF(E41&lt;0,ATAN(E41)+PI(),ATAN(E41))</f>
         <v>2.5850990081201988</v>
       </c>
       <c r="G41" s="4">
-        <f t="shared" ref="G41:G76" si="6">(D41+F41)/(4*PI())</f>
+        <f t="shared" ref="G41:G76" si="7">(D41+F41)/(4*PI())</f>
         <v>0.24857362297102578</v>
       </c>
       <c r="H41" s="4">
@@ -1519,1504 +1509,1504 @@
         <v>2.5</v>
       </c>
       <c r="J41" s="4">
-        <f t="shared" ref="J41:J76" si="7">G41*$B$14</f>
-        <v>64.629141972466698</v>
+        <f t="shared" ref="J41:J76" si="8">G41*$B$14</f>
+        <v>62.143405742756443</v>
       </c>
       <c r="K41" s="4">
         <f t="shared" si="0"/>
-        <v>258.51656788986679</v>
+        <v>248.57362297102577</v>
       </c>
       <c r="L41" s="4">
         <v>23000</v>
       </c>
       <c r="M41" s="3">
-        <f>100*$B$12*K41/L41</f>
-        <v>0.11239850777820296</v>
+        <f t="shared" si="1"/>
+        <v>0.10807548824827208</v>
       </c>
       <c r="N41" s="3">
-        <f t="shared" ref="N41:N104" si="8">M41</f>
-        <v>0.11239850777820296</v>
+        <f t="shared" ref="N41:N104" si="9">M41</f>
+        <v>0.10807548824827208</v>
       </c>
     </row>
     <row r="42" spans="1:14">
       <c r="A42" s="24">
-        <f t="shared" ref="A42:A104" si="9">A41+$B$12</f>
+        <f t="shared" ref="A42:A104" si="10">A41+$B$12</f>
         <v>0.30000000000000004</v>
       </c>
       <c r="B42" s="13">
-        <f t="shared" si="1"/>
-        <v>3.333333333333333</v>
-      </c>
-      <c r="C42" s="4">
         <f t="shared" si="2"/>
         <v>3.333333333333333</v>
       </c>
+      <c r="C42" s="4">
+        <f t="shared" si="3"/>
+        <v>3.333333333333333</v>
+      </c>
       <c r="D42" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.76152051067824744</v>
       </c>
       <c r="E42" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.0683704122281781</v>
       </c>
       <c r="F42" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.3231513144788307</v>
       </c>
       <c r="G42" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.24547038439502383</v>
       </c>
       <c r="H42" s="4">
         <v>15</v>
       </c>
       <c r="I42" s="4">
-        <f t="shared" ref="I42:I76" si="10">I41+(A42-A41)*H42</f>
+        <f t="shared" ref="I42:I76" si="11">I41+(A42-A41)*H42</f>
         <v>4</v>
       </c>
       <c r="J42" s="4">
-        <f t="shared" si="7"/>
-        <v>63.822299942706195</v>
+        <f t="shared" si="8"/>
+        <v>61.367596098755961</v>
       </c>
       <c r="K42" s="4">
         <f t="shared" si="0"/>
-        <v>255.28919977082478</v>
+        <v>245.47038439502384</v>
       </c>
       <c r="L42" s="4">
         <v>23000</v>
       </c>
       <c r="M42" s="3">
-        <f>100*$B$12*K42/L42</f>
-        <v>0.11099530424818468</v>
+        <f t="shared" si="1"/>
+        <v>0.10672625408479297</v>
       </c>
       <c r="N42" s="3">
-        <f t="shared" si="8"/>
-        <v>0.11099530424818468</v>
+        <f t="shared" si="9"/>
+        <v>0.10672625408479297</v>
       </c>
     </row>
     <row r="43" spans="1:14">
       <c r="A43" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.4</v>
       </c>
       <c r="B43" s="13">
-        <f t="shared" si="1"/>
-        <v>2.5</v>
-      </c>
-      <c r="C43" s="4">
         <f t="shared" si="2"/>
         <v>2.5</v>
       </c>
+      <c r="C43" s="4">
+        <f t="shared" si="3"/>
+        <v>2.5</v>
+      </c>
       <c r="D43" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.93850181715830594</v>
       </c>
       <c r="E43" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-1.7966917428727469</v>
       </c>
       <c r="F43" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>2.0786761777120915</v>
       </c>
       <c r="G43" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.2400993960358585</v>
       </c>
       <c r="H43" s="4">
         <v>15</v>
       </c>
       <c r="I43" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>5.5</v>
       </c>
       <c r="J43" s="4">
-        <f t="shared" si="7"/>
-        <v>62.425842969323213</v>
+        <f t="shared" si="8"/>
+        <v>60.024849008964622</v>
       </c>
       <c r="K43" s="4">
         <f t="shared" si="0"/>
-        <v>249.70337187729285</v>
+        <v>240.09939603585849</v>
       </c>
       <c r="L43" s="4">
         <v>23000</v>
       </c>
       <c r="M43" s="3">
-        <f>100*$B$12*K43/L43</f>
-        <v>0.10856668342490992</v>
+        <f t="shared" si="1"/>
+        <v>0.10439104175472108</v>
       </c>
       <c r="N43" s="3">
-        <f t="shared" si="8"/>
-        <v>0.10856668342490992</v>
+        <f t="shared" si="9"/>
+        <v>0.10439104175472108</v>
       </c>
     </row>
     <row r="44" spans="1:14">
       <c r="A44" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.5</v>
       </c>
       <c r="B44" s="13">
-        <f t="shared" si="1"/>
-        <v>2</v>
-      </c>
-      <c r="C44" s="4">
         <f t="shared" si="2"/>
         <v>2</v>
       </c>
+      <c r="C44" s="4">
+        <f t="shared" si="3"/>
+        <v>2</v>
+      </c>
       <c r="D44" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.0666666666666667</v>
       </c>
       <c r="E44" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-3.4285714285714284</v>
       </c>
       <c r="F44" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.8545904360032244</v>
       </c>
       <c r="G44" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.23246625396611079</v>
       </c>
       <c r="H44" s="4">
         <v>15</v>
       </c>
       <c r="I44" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>7</v>
       </c>
       <c r="J44" s="4">
-        <f t="shared" si="7"/>
-        <v>60.441226031188805</v>
+        <f t="shared" si="8"/>
+        <v>58.1165634915277</v>
       </c>
       <c r="K44" s="4">
         <f t="shared" si="0"/>
-        <v>241.76490412475522</v>
+        <v>232.4662539661108</v>
       </c>
       <c r="L44" s="4">
         <v>23000</v>
       </c>
       <c r="M44" s="3">
-        <f>100*$B$12*K44/L44</f>
-        <v>0.10511517570641532</v>
+        <f t="shared" si="1"/>
+        <v>0.10107228433309165</v>
       </c>
       <c r="N44" s="3">
-        <f t="shared" si="8"/>
-        <v>0.10511517570641532</v>
+        <f t="shared" si="9"/>
+        <v>0.10107228433309165</v>
       </c>
     </row>
     <row r="45" spans="1:14">
       <c r="A45" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.6</v>
       </c>
       <c r="B45" s="13">
-        <f t="shared" si="1"/>
-        <v>1.6666666666666667</v>
-      </c>
-      <c r="C45" s="4">
         <f t="shared" si="2"/>
         <v>1.6666666666666667</v>
       </c>
+      <c r="C45" s="4">
+        <f t="shared" si="3"/>
+        <v>1.6666666666666667</v>
+      </c>
       <c r="D45" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.1487256851249164</v>
       </c>
       <c r="E45" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>-12.257147470003083</v>
       </c>
       <c r="F45" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.6522010838541537</v>
       </c>
       <c r="G45" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.2228906702607151</v>
       </c>
       <c r="H45" s="4">
         <v>15</v>
       </c>
       <c r="I45" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>8.5</v>
       </c>
       <c r="J45" s="4">
-        <f t="shared" si="7"/>
-        <v>57.951574267785929</v>
+        <f t="shared" si="8"/>
+        <v>55.722667565178774</v>
       </c>
       <c r="K45" s="4">
         <f t="shared" si="0"/>
-        <v>231.80629707114372</v>
+        <v>222.8906702607151</v>
       </c>
       <c r="L45" s="4">
         <v>23000</v>
       </c>
       <c r="M45" s="3">
-        <f>100*$B$12*K45/L45</f>
-        <v>0.10078534655267118</v>
+        <f t="shared" si="1"/>
+        <v>9.6908987069876135E-2</v>
       </c>
       <c r="N45" s="3">
-        <f t="shared" si="8"/>
-        <v>0.10078534655267118</v>
+        <f t="shared" si="9"/>
+        <v>9.6908987069876135E-2</v>
       </c>
     </row>
     <row r="46" spans="1:14">
       <c r="A46" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.7</v>
       </c>
       <c r="B46" s="13">
-        <f t="shared" si="1"/>
-        <v>1.4285714285714286</v>
-      </c>
-      <c r="C46" s="4">
         <f t="shared" si="2"/>
         <v>1.4285714285714286</v>
       </c>
+      <c r="C46" s="4">
+        <f t="shared" si="3"/>
+        <v>1.4285714285714286</v>
+      </c>
       <c r="D46" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.1908912090392874</v>
       </c>
       <c r="E46" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>10.037086493995142</v>
       </c>
       <c r="F46" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.4714935239229767</v>
       </c>
       <c r="G46" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.21186584533167005</v>
       </c>
       <c r="H46" s="4">
         <v>15</v>
       </c>
       <c r="I46" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>10</v>
       </c>
       <c r="J46" s="4">
-        <f t="shared" si="7"/>
-        <v>55.085119786234216</v>
+        <f t="shared" si="8"/>
+        <v>52.966461332917511</v>
       </c>
       <c r="K46" s="4">
         <f t="shared" si="0"/>
-        <v>220.34047914493686</v>
+        <v>211.86584533167004</v>
       </c>
       <c r="L46" s="4">
         <v>23000</v>
       </c>
       <c r="M46" s="3">
-        <f>100*$B$12*K46/L46</f>
-        <v>9.5800208323885583E-2</v>
+        <f t="shared" si="1"/>
+        <v>9.2115584926813071E-2</v>
       </c>
       <c r="N46" s="3">
-        <f t="shared" si="8"/>
-        <v>9.5800208323885583E-2</v>
+        <f t="shared" si="9"/>
+        <v>9.2115584926813071E-2</v>
       </c>
     </row>
     <row r="47" spans="1:14">
       <c r="A47" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.79999999999999993</v>
       </c>
       <c r="B47" s="13">
-        <f t="shared" si="1"/>
-        <v>1.25</v>
-      </c>
-      <c r="C47" s="4">
         <f t="shared" si="2"/>
         <v>1.25</v>
       </c>
+      <c r="C47" s="4">
+        <f t="shared" si="3"/>
+        <v>1.25</v>
+      </c>
       <c r="D47" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2008925949203193</v>
       </c>
       <c r="E47" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3.7698554081837408</v>
       </c>
       <c r="F47" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.3115056515155326</v>
       </c>
       <c r="G47" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.19993029996783782</v>
       </c>
       <c r="H47" s="4">
         <v>15</v>
       </c>
       <c r="I47" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>11.5</v>
       </c>
       <c r="J47" s="4">
-        <f t="shared" si="7"/>
-        <v>51.98187799163783</v>
+        <f t="shared" si="8"/>
+        <v>49.982574991959453</v>
       </c>
       <c r="K47" s="4">
         <f t="shared" si="0"/>
-        <v>207.92751196655132</v>
+        <v>199.93029996783781</v>
       </c>
       <c r="L47" s="4">
         <v>23000</v>
       </c>
       <c r="M47" s="3">
-        <f>100*$B$12*K47/L47</f>
-        <v>9.0403266072413613E-2</v>
+        <f t="shared" si="1"/>
+        <v>8.6926217377320786E-2</v>
       </c>
       <c r="N47" s="3">
-        <f t="shared" si="8"/>
-        <v>9.0403266072413613E-2</v>
+        <f t="shared" si="9"/>
+        <v>8.6926217377320786E-2</v>
       </c>
     </row>
     <row r="48" spans="1:14">
       <c r="A48" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.89999999999999991</v>
       </c>
       <c r="B48" s="13">
-        <f t="shared" si="1"/>
-        <v>1.1111111111111112</v>
-      </c>
-      <c r="C48" s="4">
         <f t="shared" si="2"/>
         <v>1.1111111111111112</v>
       </c>
+      <c r="C48" s="4">
+        <f t="shared" si="3"/>
+        <v>1.1111111111111112</v>
+      </c>
       <c r="D48" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.1865082599882966</v>
       </c>
       <c r="E48" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2.3645089182377856</v>
       </c>
       <c r="F48" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.1706880989433199</v>
       </c>
       <c r="G48" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.18757972618109217</v>
       </c>
       <c r="H48" s="4">
         <v>15</v>
       </c>
       <c r="I48" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>13</v>
       </c>
       <c r="J48" s="4">
-        <f t="shared" si="7"/>
-        <v>48.770728807083962</v>
+        <f t="shared" si="8"/>
+        <v>46.894931545273046</v>
       </c>
       <c r="K48" s="4">
         <f t="shared" si="0"/>
-        <v>195.08291522833585</v>
+        <v>187.57972618109218</v>
       </c>
       <c r="L48" s="4">
         <v>23000</v>
       </c>
       <c r="M48" s="3">
-        <f>100*$B$12*K48/L48</f>
-        <v>8.4818658794928628E-2</v>
+        <f t="shared" si="1"/>
+        <v>8.1556402687431376E-2</v>
       </c>
       <c r="N48" s="3">
-        <f t="shared" si="8"/>
-        <v>8.4818658794928628E-2</v>
+        <f t="shared" si="9"/>
+        <v>8.1556402687431376E-2</v>
       </c>
     </row>
     <row r="49" spans="1:14">
       <c r="A49" s="24">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>0.99999999999999989</v>
       </c>
       <c r="B49" s="13">
-        <f t="shared" si="1"/>
-        <v>1</v>
-      </c>
-      <c r="C49" s="4">
         <f t="shared" si="2"/>
         <v>1</v>
       </c>
+      <c r="C49" s="4">
+        <f t="shared" si="3"/>
+        <v>1</v>
+      </c>
       <c r="D49" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.1547005383792515</v>
       </c>
       <c r="E49" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.7320508075688772</v>
       </c>
       <c r="F49" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>1.0471975511965976</v>
       </c>
       <c r="G49" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.17522148257029865</v>
       </c>
       <c r="H49" s="4">
         <v>15</v>
       </c>
       <c r="I49" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>14.5</v>
       </c>
       <c r="J49" s="4">
-        <f t="shared" si="7"/>
-        <v>45.557585468277651</v>
+        <f t="shared" si="8"/>
+        <v>43.805370642574665</v>
       </c>
       <c r="K49" s="4">
         <f t="shared" si="0"/>
-        <v>182.2303418731106</v>
+        <v>175.22148257029866</v>
       </c>
       <c r="L49" s="4">
         <v>23000</v>
       </c>
       <c r="M49" s="3">
-        <f>100*$B$12*K49/L49</f>
-        <v>7.9230583423091555E-2</v>
+        <f t="shared" si="1"/>
+        <v>7.6183253291434203E-2</v>
       </c>
       <c r="N49" s="3">
-        <f t="shared" si="8"/>
-        <v>7.9230583423091555E-2</v>
+        <f t="shared" si="9"/>
+        <v>7.6183253291434203E-2</v>
       </c>
     </row>
     <row r="50" spans="1:14">
       <c r="A50" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.0999999999999999</v>
       </c>
       <c r="B50" s="13">
-        <f t="shared" si="1"/>
-        <v>0.90909090909090917</v>
-      </c>
-      <c r="C50" s="4">
         <f t="shared" si="2"/>
         <v>0.90909090909090917</v>
       </c>
+      <c r="C50" s="4">
+        <f t="shared" si="3"/>
+        <v>0.90909090909090917</v>
+      </c>
       <c r="D50" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.111240053220891</v>
       </c>
       <c r="E50" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.3666738430627101</v>
       </c>
       <c r="F50" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.93910819487140595</v>
       </c>
       <c r="G50" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.16316152937184841</v>
       </c>
       <c r="H50" s="4">
         <v>15</v>
       </c>
       <c r="I50" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>16</v>
       </c>
       <c r="J50" s="4">
-        <f t="shared" si="7"/>
-        <v>42.421997636680587</v>
+        <f t="shared" si="8"/>
+        <v>40.790382342962104</v>
       </c>
       <c r="K50" s="4">
         <f t="shared" si="0"/>
-        <v>169.68799054672235</v>
+        <v>163.16152937184842</v>
       </c>
       <c r="L50" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M50" s="3">
-        <f>100*$B$12*K50/L50</f>
-        <v>3.2016601989947616E-2</v>
+        <f t="shared" si="1"/>
+        <v>7.093979537906453E-2</v>
       </c>
       <c r="N50" s="3">
-        <f t="shared" si="8"/>
-        <v>3.2016601989947616E-2</v>
+        <f t="shared" si="9"/>
+        <v>7.093979537906453E-2</v>
       </c>
     </row>
     <row r="51" spans="1:14">
       <c r="A51" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.2</v>
       </c>
       <c r="B51" s="13">
-        <f t="shared" si="1"/>
-        <v>0.83333333333333337</v>
-      </c>
-      <c r="C51" s="4">
         <f t="shared" si="2"/>
         <v>0.83333333333333337</v>
       </c>
+      <c r="C51" s="4">
+        <f t="shared" si="3"/>
+        <v>0.83333333333333337</v>
+      </c>
       <c r="D51" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.0606502282305417</v>
       </c>
       <c r="E51" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1.1258945967821576</v>
       </c>
       <c r="F51" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.84454866728068156</v>
       </c>
       <c r="G51" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.15161091089691531</v>
       </c>
       <c r="H51" s="4">
         <v>15</v>
       </c>
       <c r="I51" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>17.5</v>
       </c>
       <c r="J51" s="4">
-        <f t="shared" si="7"/>
-        <v>39.418836833197979</v>
+        <f t="shared" si="8"/>
+        <v>37.902727724228825</v>
       </c>
       <c r="K51" s="4">
         <f t="shared" si="0"/>
-        <v>157.67534733279192</v>
+        <v>151.6109108969153</v>
       </c>
       <c r="L51" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M51" s="3">
-        <f>100*$B$12*K51/L51</f>
-        <v>2.9750065534489042E-2</v>
+        <f t="shared" si="1"/>
+        <v>6.5917787346484916E-2</v>
       </c>
       <c r="N51" s="3">
-        <f t="shared" si="8"/>
-        <v>2.9750065534489042E-2</v>
+        <f t="shared" si="9"/>
+        <v>6.5917787346484916E-2</v>
       </c>
     </row>
     <row r="52" spans="1:14">
       <c r="A52" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.3</v>
       </c>
       <c r="B52" s="13">
-        <f t="shared" si="1"/>
-        <v>0.76923076923076916</v>
-      </c>
-      <c r="C52" s="4">
         <f t="shared" si="2"/>
         <v>0.76923076923076916</v>
       </c>
+      <c r="C52" s="4">
+        <f t="shared" si="3"/>
+        <v>0.76923076923076916</v>
+      </c>
       <c r="D52" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.006324116258676</v>
       </c>
       <c r="E52" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.95384673806795539</v>
       </c>
       <c r="F52" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.76178081429612787</v>
       </c>
       <c r="G52" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.14070131980147471</v>
       </c>
       <c r="H52" s="4">
         <v>15</v>
       </c>
       <c r="I52" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>19</v>
       </c>
       <c r="J52" s="4">
-        <f t="shared" si="7"/>
-        <v>36.582343148383423</v>
+        <f t="shared" si="8"/>
+        <v>35.175329950368678</v>
       </c>
       <c r="K52" s="4">
         <f t="shared" si="0"/>
-        <v>146.32937259353369</v>
+        <v>140.70131980147471</v>
       </c>
       <c r="L52" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M52" s="3">
-        <f>100*$B$12*K52/L52</f>
-        <v>2.7609315583685602E-2</v>
+        <f t="shared" si="1"/>
+        <v>6.1174486870206393E-2</v>
       </c>
       <c r="N52" s="3">
-        <f t="shared" si="8"/>
-        <v>2.7609315583685602E-2</v>
+        <f t="shared" si="9"/>
+        <v>6.1174486870206393E-2</v>
       </c>
     </row>
     <row r="53" spans="1:14">
       <c r="A53" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.4000000000000001</v>
       </c>
       <c r="B53" s="13">
-        <f t="shared" si="1"/>
-        <v>0.71428571428571419</v>
-      </c>
-      <c r="C53" s="4">
         <f t="shared" si="2"/>
         <v>0.71428571428571419</v>
       </c>
+      <c r="C53" s="4">
+        <f t="shared" si="3"/>
+        <v>0.71428571428571419</v>
+      </c>
       <c r="D53" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.95071144686682219</v>
       </c>
       <c r="E53" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.82405490531783476</v>
       </c>
       <c r="F53" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.68923743662665893</v>
       </c>
       <c r="G53" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.13050298561301113</v>
       </c>
       <c r="H53" s="4">
         <v>15</v>
       </c>
       <c r="I53" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>20.5</v>
       </c>
       <c r="J53" s="4">
-        <f t="shared" si="7"/>
-        <v>33.930776259382895</v>
+        <f t="shared" si="8"/>
+        <v>32.625746403252784</v>
       </c>
       <c r="K53" s="4">
         <f t="shared" si="0"/>
-        <v>135.72310503753158</v>
+        <v>130.50298561301113</v>
       </c>
       <c r="L53" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M53" s="3">
-        <f>100*$B$12*K53/L53</f>
-        <v>2.5608133025949355E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.6740428527396143E-2</v>
       </c>
       <c r="N53" s="3">
-        <f t="shared" si="8"/>
-        <v>2.5608133025949355E-2</v>
+        <f t="shared" si="9"/>
+        <v>5.6740428527396143E-2</v>
       </c>
     </row>
     <row r="54" spans="1:14">
       <c r="A54" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.5000000000000002</v>
       </c>
       <c r="B54" s="13">
-        <f t="shared" si="1"/>
-        <v>0.66666666666666652</v>
-      </c>
-      <c r="C54" s="4">
         <f t="shared" si="2"/>
         <v>0.66666666666666652</v>
       </c>
+      <c r="C54" s="4">
+        <f t="shared" si="3"/>
+        <v>0.66666666666666652</v>
+      </c>
       <c r="D54" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.89551615398030626</v>
       </c>
       <c r="E54" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.72229587602061174</v>
       </c>
       <c r="F54" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.62553344388308973</v>
       </c>
       <c r="G54" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.12104128109394954</v>
       </c>
       <c r="H54" s="4">
         <v>15</v>
       </c>
       <c r="I54" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>22</v>
       </c>
       <c r="J54" s="4">
-        <f t="shared" si="7"/>
-        <v>31.470733084426882</v>
+        <f t="shared" si="8"/>
+        <v>30.260320273487388</v>
       </c>
       <c r="K54" s="4">
         <f t="shared" si="0"/>
-        <v>125.88293233770753</v>
+        <v>121.04128109394955</v>
       </c>
       <c r="L54" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M54" s="3">
-        <f>100*$B$12*K54/L54</f>
-        <v>2.3751496667491986E-2</v>
+        <f t="shared" si="1"/>
+        <v>5.2626643953891113E-2</v>
       </c>
       <c r="N54" s="3">
-        <f t="shared" si="8"/>
-        <v>2.3751496667491986E-2</v>
+        <f t="shared" si="9"/>
+        <v>5.2626643953891113E-2</v>
       </c>
     </row>
     <row r="55" spans="1:14">
       <c r="A55" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.6000000000000003</v>
       </c>
       <c r="B55" s="13">
-        <f t="shared" si="1"/>
-        <v>0.62499999999999989</v>
-      </c>
-      <c r="C55" s="4">
         <f t="shared" si="2"/>
         <v>0.62499999999999989</v>
       </c>
+      <c r="C55" s="4">
+        <f t="shared" si="3"/>
+        <v>0.62499999999999989</v>
+      </c>
       <c r="D55" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.841874886815006</v>
       </c>
       <c r="E55" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.64020855955816569</v>
       </c>
       <c r="F55" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.56946113364432815</v>
       </c>
       <c r="G55" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.11231055200987368</v>
       </c>
       <c r="H55" s="4">
         <v>15</v>
       </c>
       <c r="I55" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>23.5</v>
       </c>
       <c r="J55" s="4">
-        <f t="shared" si="7"/>
-        <v>29.200743522567155</v>
+        <f t="shared" si="8"/>
+        <v>28.077638002468419</v>
       </c>
       <c r="K55" s="4">
         <f t="shared" si="0"/>
-        <v>116.80297409026862</v>
+        <v>112.31055200987367</v>
       </c>
       <c r="L55" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M55" s="3">
-        <f>100*$B$12*K55/L55</f>
-        <v>2.2038296998163891E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.883067478690159E-2</v>
       </c>
       <c r="N55" s="3">
-        <f t="shared" si="8"/>
-        <v>2.2038296998163891E-2</v>
+        <f t="shared" si="9"/>
+        <v>4.883067478690159E-2</v>
       </c>
     </row>
     <row r="56" spans="1:14">
       <c r="A56" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.7000000000000004</v>
       </c>
       <c r="B56" s="13">
-        <f t="shared" si="1"/>
-        <v>0.58823529411764697</v>
-      </c>
-      <c r="C56" s="4">
         <f t="shared" si="2"/>
         <v>0.58823529411764697</v>
       </c>
+      <c r="C56" s="4">
+        <f t="shared" si="3"/>
+        <v>0.58823529411764697</v>
+      </c>
       <c r="D56" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.79050547434285723</v>
       </c>
       <c r="E56" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.57253120915532407</v>
       </c>
       <c r="F56" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.51997693863769834</v>
       </c>
       <c r="G56" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>0.104284876930425</v>
       </c>
       <c r="H56" s="4">
         <v>15</v>
       </c>
       <c r="I56" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>25</v>
       </c>
       <c r="J56" s="4">
-        <f t="shared" si="7"/>
-        <v>27.1140680019105</v>
+        <f t="shared" si="8"/>
+        <v>26.07121923260625</v>
       </c>
       <c r="K56" s="4">
         <f t="shared" si="0"/>
-        <v>108.456272007642</v>
+        <v>104.284876930425</v>
       </c>
       <c r="L56" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M56" s="3">
-        <f>100*$B$12*K56/L56</f>
-        <v>2.0463447548611697E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.5341250839315221E-2</v>
       </c>
       <c r="N56" s="3">
-        <f t="shared" si="8"/>
-        <v>2.0463447548611697E-2</v>
+        <f t="shared" si="9"/>
+        <v>4.5341250839315221E-2</v>
       </c>
     </row>
     <row r="57" spans="1:14">
       <c r="A57" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.8000000000000005</v>
       </c>
       <c r="B57" s="13">
-        <f t="shared" si="1"/>
-        <v>0.55555555555555536</v>
-      </c>
-      <c r="C57" s="4">
         <f t="shared" si="2"/>
         <v>0.55555555555555536</v>
       </c>
+      <c r="C57" s="4">
+        <f t="shared" si="3"/>
+        <v>0.55555555555555536</v>
+      </c>
       <c r="D57" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.7418241990518244</v>
       </c>
       <c r="E57" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.5157706202700596</v>
       </c>
       <c r="F57" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.47618435929988184</v>
       </c>
       <c r="G57" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.6926041394953644E-2</v>
       </c>
       <c r="H57" s="4">
         <v>15</v>
       </c>
       <c r="I57" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>26.5</v>
       </c>
       <c r="J57" s="4">
-        <f t="shared" si="7"/>
-        <v>25.200770762687949</v>
+        <f t="shared" si="8"/>
+        <v>24.231510348738411</v>
       </c>
       <c r="K57" s="4">
         <f t="shared" si="0"/>
-        <v>100.80308305075179</v>
+        <v>96.926041394953643</v>
       </c>
       <c r="L57" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M57" s="3">
-        <f>100*$B$12*K57/L57</f>
-        <v>1.9019449632217321E-2</v>
+        <f t="shared" si="1"/>
+        <v>4.2141757128240712E-2</v>
       </c>
       <c r="N57" s="3">
-        <f t="shared" si="8"/>
-        <v>1.9019449632217321E-2</v>
+        <f t="shared" si="9"/>
+        <v>4.2141757128240712E-2</v>
       </c>
     </row>
     <row r="58" spans="1:14">
       <c r="A58" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>1.9000000000000006</v>
       </c>
       <c r="B58" s="13">
-        <f t="shared" si="1"/>
-        <v>0.52631578947368407</v>
-      </c>
-      <c r="C58" s="4">
         <f t="shared" si="2"/>
         <v>0.52631578947368407</v>
       </c>
+      <c r="C58" s="4">
+        <f t="shared" si="3"/>
+        <v>0.52631578947368407</v>
+      </c>
       <c r="D58" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.69603525271099598</v>
       </c>
       <c r="E58" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.46750570870546715</v>
       </c>
       <c r="F58" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.4373159326179063</v>
       </c>
       <c r="G58" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>9.0189221702076786E-2</v>
       </c>
       <c r="H58" s="4">
         <v>15</v>
       </c>
       <c r="I58" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>28</v>
       </c>
       <c r="J58" s="4">
-        <f t="shared" si="7"/>
-        <v>23.449197642539964</v>
+        <f t="shared" si="8"/>
+        <v>22.547305425519195</v>
       </c>
       <c r="K58" s="4">
         <f t="shared" si="0"/>
-        <v>93.796790570159857</v>
+        <v>90.189221702076779</v>
       </c>
       <c r="L58" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M58" s="3">
-        <f>100*$B$12*K58/L58</f>
-        <v>1.7697507654747143E-2</v>
+        <f t="shared" si="1"/>
+        <v>3.921270508785947E-2</v>
       </c>
       <c r="N58" s="3">
-        <f t="shared" si="8"/>
-        <v>1.7697507654747143E-2</v>
+        <f t="shared" si="9"/>
+        <v>3.921270508785947E-2</v>
       </c>
     </row>
     <row r="59" spans="1:14">
       <c r="A59" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.0000000000000004</v>
       </c>
       <c r="B59" s="13">
-        <f t="shared" si="1"/>
-        <v>0.49999999999999989</v>
-      </c>
-      <c r="C59" s="4">
         <f t="shared" si="2"/>
         <v>0.49999999999999989</v>
       </c>
+      <c r="C59" s="4">
+        <f t="shared" si="3"/>
+        <v>0.49999999999999989</v>
+      </c>
       <c r="D59" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.65319726474218076</v>
       </c>
       <c r="E59" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.42599821613620475</v>
       </c>
       <c r="F59" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.40271584158066148</v>
       </c>
       <c r="G59" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>8.4026895173399188E-2</v>
       </c>
       <c r="H59" s="4">
         <v>15</v>
       </c>
       <c r="I59" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>29.499999999999996</v>
       </c>
       <c r="J59" s="4">
-        <f t="shared" si="7"/>
-        <v>21.846992745083789</v>
+        <f t="shared" si="8"/>
+        <v>21.006723793349796</v>
       </c>
       <c r="K59" s="4">
         <f t="shared" si="0"/>
-        <v>87.387970980335155</v>
+        <v>84.026895173399183</v>
       </c>
       <c r="L59" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M59" s="3">
-        <f>100*$B$12*K59/L59</f>
-        <v>1.6488296411383989E-2</v>
+        <f t="shared" si="1"/>
+        <v>3.6533432684086597E-2</v>
       </c>
       <c r="N59" s="3">
-        <f t="shared" si="8"/>
-        <v>1.6488296411383989E-2</v>
+        <f t="shared" si="9"/>
+        <v>3.6533432684086597E-2</v>
       </c>
     </row>
     <row r="60" spans="1:14">
       <c r="A60" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.1000000000000005</v>
       </c>
       <c r="B60" s="13">
-        <f t="shared" si="1"/>
-        <v>0.47619047619047605</v>
-      </c>
-      <c r="C60" s="4">
         <f t="shared" si="2"/>
         <v>0.47619047619047605</v>
       </c>
+      <c r="C60" s="4">
+        <f t="shared" si="3"/>
+        <v>0.47619047619047605</v>
+      </c>
       <c r="D60" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.61327181575603129</v>
       </c>
       <c r="E60" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.38996302188214838</v>
       </c>
       <c r="F60" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.37182397717232046</v>
       </c>
       <c r="G60" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.8391432431788671E-2</v>
       </c>
       <c r="H60" s="4">
         <v>15</v>
       </c>
       <c r="I60" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>30.999999999999996</v>
       </c>
       <c r="J60" s="4">
-        <f t="shared" si="7"/>
-        <v>20.381772432265056</v>
+        <f t="shared" si="8"/>
+        <v>19.597858107947168</v>
       </c>
       <c r="K60" s="4">
         <f t="shared" si="0"/>
-        <v>81.527089729060222</v>
+        <v>78.391432431788672</v>
       </c>
       <c r="L60" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M60" s="3">
-        <f>100*$B$12*K60/L60</f>
-        <v>1.5382469760200041E-2</v>
+        <f t="shared" si="1"/>
+        <v>3.4083231492082026E-2</v>
       </c>
       <c r="N60" s="3">
-        <f t="shared" si="8"/>
-        <v>1.5382469760200041E-2</v>
+        <f t="shared" si="9"/>
+        <v>3.4083231492082026E-2</v>
       </c>
     </row>
     <row r="61" spans="1:14">
       <c r="A61" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.2000000000000006</v>
       </c>
       <c r="B61" s="13">
-        <f t="shared" si="1"/>
-        <v>0.45454545454545442</v>
-      </c>
-      <c r="C61" s="4">
         <f t="shared" si="2"/>
         <v>0.45454545454545442</v>
       </c>
+      <c r="C61" s="4">
+        <f t="shared" si="3"/>
+        <v>0.45454545454545442</v>
+      </c>
       <c r="D61" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.57615823574798608</v>
       </c>
       <c r="E61" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.3584263558677418</v>
       </c>
       <c r="F61" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.34416178391420521</v>
       </c>
       <c r="G61" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>7.323674017783402E-2</v>
       </c>
       <c r="H61" s="4">
         <v>15</v>
       </c>
       <c r="I61" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>32.5</v>
       </c>
       <c r="J61" s="4">
-        <f t="shared" si="7"/>
-        <v>19.041552446236846</v>
+        <f t="shared" si="8"/>
+        <v>18.309185044458506</v>
       </c>
       <c r="K61" s="4">
         <f t="shared" si="0"/>
-        <v>76.166209784947384</v>
+        <v>73.236740177834022</v>
       </c>
       <c r="L61" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M61" s="3">
-        <f>100*$B$12*K61/L61</f>
-        <v>1.437098297829196E-2</v>
+        <f t="shared" si="1"/>
+        <v>3.1842060946884354E-2</v>
       </c>
       <c r="N61" s="3">
-        <f t="shared" si="8"/>
-        <v>1.437098297829196E-2</v>
+        <f t="shared" si="9"/>
+        <v>3.1842060946884354E-2</v>
       </c>
     </row>
     <row r="62" spans="1:14">
       <c r="A62" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.3000000000000007</v>
       </c>
       <c r="B62" s="13">
-        <f t="shared" si="1"/>
-        <v>0.43478260869565205</v>
-      </c>
-      <c r="C62" s="4">
         <f t="shared" si="2"/>
         <v>0.43478260869565205</v>
       </c>
+      <c r="C62" s="4">
+        <f t="shared" si="3"/>
+        <v>0.43478260869565205</v>
+      </c>
       <c r="D62" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.54171818877701194</v>
       </c>
       <c r="E62" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.33063483485561995</v>
       </c>
       <c r="F62" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.3193199428489491</v>
       </c>
       <c r="G62" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.8519237419440854E-2</v>
       </c>
       <c r="H62" s="4">
         <v>15</v>
       </c>
       <c r="I62" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>34</v>
       </c>
       <c r="J62" s="4">
-        <f t="shared" si="7"/>
-        <v>17.815001729054622</v>
+        <f t="shared" si="8"/>
+        <v>17.129809354860214</v>
       </c>
       <c r="K62" s="4">
         <f t="shared" si="0"/>
-        <v>71.260006916218487</v>
+        <v>68.519237419440856</v>
       </c>
       <c r="L62" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M62" s="3">
-        <f>100*$B$12*K62/L62</f>
-        <v>1.3445284323814808E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.9790972791061243E-2</v>
       </c>
       <c r="N62" s="3">
-        <f t="shared" si="8"/>
-        <v>1.3445284323814808E-2</v>
+        <f t="shared" si="9"/>
+        <v>2.9790972791061243E-2</v>
       </c>
     </row>
     <row r="63" spans="1:14">
       <c r="A63" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.4000000000000008</v>
       </c>
       <c r="B63" s="13">
-        <f t="shared" si="1"/>
-        <v>0.41666666666666652</v>
-      </c>
-      <c r="C63" s="4">
         <f t="shared" si="2"/>
         <v>0.41666666666666652</v>
       </c>
+      <c r="C63" s="4">
+        <f t="shared" si="3"/>
+        <v>0.41666666666666652</v>
+      </c>
       <c r="D63" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.509792775349873</v>
       </c>
       <c r="E63" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.30599512893378</v>
       </c>
       <c r="F63" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.29694779713815811</v>
       </c>
       <c r="G63" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.4198374952127824E-2</v>
       </c>
       <c r="H63" s="4">
         <v>15</v>
       </c>
       <c r="I63" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>35.5</v>
       </c>
       <c r="J63" s="4">
-        <f t="shared" si="7"/>
-        <v>16.691577487553236</v>
+        <f t="shared" si="8"/>
+        <v>16.049593738031955</v>
       </c>
       <c r="K63" s="4">
         <f t="shared" si="0"/>
-        <v>66.766309950212943</v>
+        <v>64.198374952127821</v>
       </c>
       <c r="L63" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M63" s="3">
-        <f>100*$B$12*K63/L63</f>
-        <v>1.2597416971738291E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.791233693570775E-2</v>
       </c>
       <c r="N63" s="3">
-        <f t="shared" si="8"/>
-        <v>1.2597416971738291E-2</v>
+        <f t="shared" si="9"/>
+        <v>2.791233693570775E-2</v>
       </c>
     </row>
     <row r="64" spans="1:14">
       <c r="A64" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.5000000000000009</v>
       </c>
       <c r="B64" s="13">
-        <f t="shared" si="1"/>
-        <v>0.39999999999999986</v>
-      </c>
-      <c r="C64" s="4">
         <f t="shared" si="2"/>
         <v>0.39999999999999986</v>
       </c>
+      <c r="C64" s="4">
+        <f t="shared" si="3"/>
+        <v>0.39999999999999986</v>
+      </c>
       <c r="D64" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.48021422332606278</v>
       </c>
       <c r="E64" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.28403276373488384</v>
       </c>
       <c r="F64" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.27674435477021408</v>
       </c>
       <c r="G64" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>6.0236849709917481E-2</v>
       </c>
       <c r="H64" s="4">
         <v>15</v>
       </c>
       <c r="I64" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>37</v>
       </c>
       <c r="J64" s="4">
-        <f t="shared" si="7"/>
-        <v>15.661580924578544</v>
+        <f t="shared" si="8"/>
+        <v>15.05921242747937</v>
       </c>
       <c r="K64" s="4">
         <f t="shared" si="0"/>
-        <v>62.646323698314177</v>
+        <v>60.236849709917479</v>
       </c>
       <c r="L64" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M64" s="3">
-        <f>100*$B$12*K64/L64</f>
-        <v>1.1820061075153617E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.618993465648586E-2</v>
       </c>
       <c r="N64" s="3">
-        <f t="shared" si="8"/>
-        <v>1.1820061075153617E-2</v>
+        <f t="shared" si="9"/>
+        <v>2.618993465648586E-2</v>
       </c>
     </row>
     <row r="65" spans="1:14">
       <c r="A65" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.600000000000001</v>
       </c>
       <c r="B65" s="13">
-        <f t="shared" si="1"/>
-        <v>0.38461538461538447</v>
-      </c>
-      <c r="C65" s="4">
         <f t="shared" si="2"/>
         <v>0.38461538461538447</v>
       </c>
+      <c r="C65" s="4">
+        <f t="shared" si="3"/>
+        <v>0.38461538461538447</v>
+      </c>
       <c r="D65" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.45281370717491309</v>
       </c>
       <c r="E65" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.26436326008675526</v>
       </c>
       <c r="F65" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.25845067781802472</v>
       </c>
       <c r="G65" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.6600621358421484E-2</v>
       </c>
       <c r="H65" s="4">
         <v>15</v>
       </c>
       <c r="I65" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>38.5</v>
       </c>
       <c r="J65" s="4">
-        <f t="shared" si="7"/>
-        <v>14.716161553189586</v>
+        <f t="shared" si="8"/>
+        <v>14.150155339605371</v>
       </c>
       <c r="K65" s="4">
         <f t="shared" si="0"/>
-        <v>58.864646212758345</v>
+        <v>56.600621358421485</v>
       </c>
       <c r="L65" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M65" s="3">
-        <f>100*$B$12*K65/L65</f>
-        <v>1.1106537021275158E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.460896580800934E-2</v>
       </c>
       <c r="N65" s="3">
-        <f t="shared" si="8"/>
-        <v>1.1106537021275158E-2</v>
+        <f t="shared" si="9"/>
+        <v>2.460896580800934E-2</v>
       </c>
     </row>
     <row r="66" spans="1:14">
       <c r="A66" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.7000000000000011</v>
       </c>
       <c r="B66" s="13">
-        <f t="shared" si="1"/>
-        <v>0.37037037037037024</v>
-      </c>
-      <c r="C66" s="4">
         <f t="shared" si="2"/>
         <v>0.37037037037037024</v>
       </c>
+      <c r="C66" s="4">
+        <f t="shared" si="3"/>
+        <v>0.37037037037037024</v>
+      </c>
       <c r="D66" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.42742642467959541</v>
       </c>
       <c r="E66" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.24667145313999611</v>
       </c>
       <c r="F66" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.24184346795973277</v>
       </c>
       <c r="G66" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.3258805838065588E-2</v>
       </c>
       <c r="H66" s="4">
         <v>15</v>
       </c>
       <c r="I66" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>40</v>
       </c>
       <c r="J66" s="4">
-        <f t="shared" si="7"/>
-        <v>13.847289517897053</v>
+        <f t="shared" si="8"/>
+        <v>13.314701459516398</v>
       </c>
       <c r="K66" s="4">
         <f t="shared" si="0"/>
-        <v>55.389158071588213</v>
+        <v>53.258805838065591</v>
       </c>
       <c r="L66" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M66" s="3">
-        <f>100*$B$12*K66/L66</f>
-        <v>1.0450784541809097E-2</v>
+        <f t="shared" si="1"/>
+        <v>2.3156002538289387E-2</v>
       </c>
       <c r="N66" s="3">
-        <f t="shared" si="8"/>
-        <v>1.0450784541809097E-2</v>
+        <f t="shared" si="9"/>
+        <v>2.3156002538289387E-2</v>
       </c>
     </row>
     <row r="67" spans="1:14">
       <c r="A67" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.8000000000000012</v>
       </c>
       <c r="B67" s="13">
-        <f t="shared" si="1"/>
-        <v>0.35714285714285698</v>
-      </c>
-      <c r="C67" s="4">
         <f t="shared" si="2"/>
         <v>0.35714285714285698</v>
       </c>
+      <c r="C67" s="4">
+        <f t="shared" si="3"/>
+        <v>0.35714285714285698</v>
+      </c>
       <c r="D67" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.40389475035686562</v>
       </c>
       <c r="E67" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.23069637114056601</v>
       </c>
       <c r="F67" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.22672967123482746</v>
       </c>
       <c r="G67" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>5.0183496965392663E-2</v>
       </c>
       <c r="H67" s="4">
         <v>15</v>
       </c>
       <c r="I67" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>41.5</v>
       </c>
       <c r="J67" s="4">
-        <f t="shared" si="7"/>
-        <v>13.047709211002092</v>
+        <f t="shared" si="8"/>
+        <v>12.545874241348166</v>
       </c>
       <c r="K67" s="4">
         <f t="shared" si="0"/>
-        <v>52.190836844008366</v>
+        <v>50.183496965392663</v>
       </c>
       <c r="L67" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M67" s="3">
-        <f>100*$B$12*K67/L67</f>
-        <v>9.8473277064166729E-3</v>
+        <f t="shared" si="1"/>
+        <v>2.1818911724083765E-2</v>
       </c>
       <c r="N67" s="3">
-        <f t="shared" si="8"/>
-        <v>9.8473277064166729E-3</v>
+        <f t="shared" si="9"/>
+        <v>2.1818911724083765E-2</v>
       </c>
     </row>
     <row r="68" spans="1:14">
       <c r="A68" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>2.9000000000000012</v>
       </c>
       <c r="B68" s="13">
-        <f t="shared" si="1"/>
-        <v>0.34482758620689641</v>
-      </c>
-      <c r="C68" s="4">
         <f t="shared" si="2"/>
         <v>0.34482758620689641</v>
       </c>
+      <c r="C68" s="4">
+        <f t="shared" si="3"/>
+        <v>0.34482758620689641</v>
+      </c>
       <c r="D68" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.38207005512940612</v>
       </c>
       <c r="E68" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.21621997864408271</v>
       </c>
       <c r="F68" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.21294194396861293</v>
       </c>
       <c r="G68" s="4">
@@ -3027,2043 +3017,2043 @@
         <v>15</v>
       </c>
       <c r="I68" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>43</v>
       </c>
       <c r="J68" s="4">
-        <f t="shared" si="7"/>
-        <v>12.310883111207213</v>
+        <f t="shared" si="8"/>
+        <v>11.837387606930013</v>
       </c>
       <c r="K68" s="4">
         <f t="shared" si="0"/>
-        <v>49.243532444828851</v>
+        <v>47.349550427720054</v>
       </c>
       <c r="L68" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M68" s="3">
-        <f>100*$B$12*K68/L68</f>
-        <v>9.2912325367601606E-3</v>
+        <f t="shared" si="1"/>
+        <v>2.0586761055530457E-2</v>
       </c>
       <c r="N68" s="3">
-        <f t="shared" si="8"/>
-        <v>9.2912325367601606E-3</v>
+        <f t="shared" si="9"/>
+        <v>2.0586761055530457E-2</v>
       </c>
     </row>
     <row r="69" spans="1:14">
       <c r="A69" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.0000000000000013</v>
       </c>
       <c r="B69" s="13">
-        <f t="shared" si="1"/>
-        <v>0.3333333333333332</v>
-      </c>
-      <c r="C69" s="4">
         <f t="shared" si="2"/>
         <v>0.3333333333333332</v>
       </c>
+      <c r="C69" s="4">
+        <f t="shared" si="3"/>
+        <v>0.3333333333333332</v>
+      </c>
       <c r="D69" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.36181361349331609</v>
       </c>
       <c r="E69" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.20305866063400391</v>
       </c>
       <c r="F69" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.20033484232311943</v>
       </c>
       <c r="G69" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.473435274733082E-2</v>
       </c>
       <c r="H69" s="4">
         <v>15</v>
       </c>
       <c r="I69" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>44.5</v>
       </c>
       <c r="J69" s="4">
-        <f t="shared" si="7"/>
-        <v>11.630931714306014</v>
+        <f t="shared" si="8"/>
+        <v>11.183588186832704</v>
       </c>
       <c r="K69" s="4">
         <f t="shared" si="0"/>
-        <v>46.523726857224055</v>
+        <v>44.734352747330817</v>
       </c>
       <c r="L69" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M69" s="3">
-        <f>100*$B$12*K69/L69</f>
-        <v>8.7780616711743507E-3</v>
+        <f t="shared" si="1"/>
+        <v>1.944971858579601E-2</v>
       </c>
       <c r="N69" s="3">
-        <f t="shared" si="8"/>
-        <v>8.7780616711743507E-3</v>
+        <f t="shared" si="9"/>
+        <v>1.944971858579601E-2</v>
       </c>
     </row>
     <row r="70" spans="1:14">
       <c r="A70" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.1000000000000014</v>
       </c>
       <c r="B70" s="13">
-        <f t="shared" si="1"/>
-        <v>0.32258064516129015</v>
-      </c>
-      <c r="C70" s="4">
         <f t="shared" si="2"/>
         <v>0.32258064516129015</v>
       </c>
+      <c r="C70" s="4">
+        <f t="shared" si="3"/>
+        <v>0.32258064516129015</v>
+      </c>
       <c r="D70" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.34299689721764764</v>
       </c>
       <c r="E70" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.19105668650931831</v>
       </c>
       <c r="F70" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.18878161780328107</v>
       </c>
       <c r="G70" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.2317589647824255E-2</v>
       </c>
       <c r="H70" s="4">
         <v>15</v>
       </c>
       <c r="I70" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>46</v>
       </c>
       <c r="J70" s="4">
-        <f t="shared" si="7"/>
-        <v>11.002573308434306</v>
+        <f t="shared" si="8"/>
+        <v>10.579397411956064</v>
       </c>
       <c r="K70" s="4">
         <f t="shared" si="0"/>
-        <v>44.010293233737222</v>
+        <v>42.317589647824256</v>
       </c>
       <c r="L70" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M70" s="3">
-        <f>100*$B$12*K70/L70</f>
-        <v>8.3038289120258915E-3</v>
+        <f t="shared" si="1"/>
+        <v>1.8398952020793155E-2</v>
       </c>
       <c r="N70" s="3">
-        <f t="shared" si="8"/>
-        <v>8.3038289120258915E-3</v>
+        <f t="shared" si="9"/>
+        <v>1.8398952020793155E-2</v>
       </c>
     </row>
     <row r="71" spans="1:14">
       <c r="A71" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.2000000000000015</v>
       </c>
       <c r="B71" s="13">
-        <f t="shared" si="1"/>
-        <v>0.31249999999999983</v>
-      </c>
-      <c r="C71" s="4">
         <f t="shared" si="2"/>
         <v>0.31249999999999983</v>
       </c>
+      <c r="C71" s="4">
+        <f t="shared" si="3"/>
+        <v>0.31249999999999983</v>
+      </c>
       <c r="D71" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.32550146646264994</v>
       </c>
       <c r="E71" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.18008112812380109</v>
       </c>
       <c r="F71" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.17817151918442453</v>
       </c>
       <c r="G71" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>4.0081022683792586E-2</v>
       </c>
       <c r="H71" s="4">
         <v>15</v>
       </c>
       <c r="I71" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>47.5</v>
       </c>
       <c r="J71" s="4">
-        <f t="shared" si="7"/>
-        <v>10.421065897786072</v>
+        <f t="shared" si="8"/>
+        <v>10.020255670948146</v>
       </c>
       <c r="K71" s="4">
         <f t="shared" si="0"/>
-        <v>41.684263591144287</v>
+        <v>40.081022683792582</v>
       </c>
       <c r="L71" s="4">
-        <v>53000</v>
+        <v>23000</v>
       </c>
       <c r="M71" s="3">
-        <f>100*$B$12*K71/L71</f>
-        <v>7.8649553945555253E-3</v>
+        <f t="shared" si="1"/>
+        <v>1.7426531601648948E-2</v>
       </c>
       <c r="N71" s="3">
-        <f t="shared" si="8"/>
-        <v>7.8649553945555253E-3</v>
+        <f t="shared" si="9"/>
+        <v>1.7426531601648948E-2</v>
       </c>
     </row>
     <row r="72" spans="1:14">
       <c r="A72" s="25">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.3000000000000016</v>
       </c>
       <c r="B72" s="13">
-        <f t="shared" si="1"/>
-        <v>0.30303030303030287</v>
-      </c>
-      <c r="C72" s="4">
         <f t="shared" si="2"/>
         <v>0.30303030303030287</v>
       </c>
+      <c r="C72" s="4">
+        <f t="shared" si="3"/>
+        <v>0.30303030303030287</v>
+      </c>
       <c r="D72" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.30921860595334943</v>
       </c>
       <c r="E72" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.17001786192316409</v>
       </c>
       <c r="F72" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.16840751730930237</v>
       </c>
       <c r="G72" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.8008279233534968E-2</v>
       </c>
       <c r="H72" s="4">
         <v>15</v>
       </c>
       <c r="I72" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>49</v>
       </c>
       <c r="J72" s="4">
-        <f t="shared" si="7"/>
-        <v>9.8821526007190919</v>
+        <f t="shared" si="8"/>
+        <v>9.5020698083837427</v>
       </c>
       <c r="K72" s="4">
-        <f t="shared" ref="K72:K103" si="11">4*J72</f>
-        <v>39.528610402876367</v>
+        <f t="shared" ref="K72:K103" si="12">4*J72</f>
+        <v>38.008279233534971</v>
       </c>
       <c r="L72" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M72" s="3">
-        <f>100*$B$12*K72/L72</f>
-        <v>1.3176203467625457E-2</v>
+        <f t="shared" ref="M72:M103" si="13">100*$B$12*K72/L72</f>
+        <v>1.6525338797189117E-2</v>
       </c>
       <c r="N72" s="3">
-        <f t="shared" si="8"/>
-        <v>1.3176203467625457E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.6525338797189117E-2</v>
       </c>
     </row>
     <row r="73" spans="1:14">
       <c r="A73" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.4000000000000017</v>
       </c>
       <c r="B73" s="13">
-        <f t="shared" si="1"/>
-        <v>0.29411764705882337</v>
-      </c>
-      <c r="C73" s="4">
         <f t="shared" si="2"/>
         <v>0.29411764705882337</v>
       </c>
+      <c r="C73" s="4">
+        <f t="shared" si="3"/>
+        <v>0.29411764705882337</v>
+      </c>
       <c r="D73" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.29404880866530758</v>
       </c>
       <c r="E73" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.16076839052034658</v>
       </c>
       <c r="F73" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.15940438297212808</v>
       </c>
       <c r="G73" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.6084658454947197E-2</v>
       </c>
       <c r="H73" s="4">
         <v>15</v>
       </c>
       <c r="I73" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>50.5</v>
       </c>
       <c r="J73" s="4">
-        <f t="shared" si="7"/>
-        <v>9.3820111982862713</v>
+        <f t="shared" si="8"/>
+        <v>9.0211646137367989</v>
       </c>
       <c r="K73" s="4">
-        <f t="shared" si="11"/>
-        <v>37.528044793145085</v>
+        <f t="shared" si="12"/>
+        <v>36.084658454947196</v>
       </c>
       <c r="L73" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M73" s="3">
-        <f>100*$B$12*K73/L73</f>
-        <v>1.2509348264381695E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.5688981936933563E-2</v>
       </c>
       <c r="N73" s="3">
-        <f t="shared" si="8"/>
-        <v>1.2509348264381695E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.5688981936933563E-2</v>
       </c>
     </row>
     <row r="74" spans="1:14">
       <c r="A74" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.5000000000000018</v>
       </c>
       <c r="B74" s="13">
-        <f t="shared" si="1"/>
-        <v>0.28571428571428559</v>
-      </c>
-      <c r="C74" s="4">
         <f t="shared" si="2"/>
         <v>0.28571428571428559</v>
       </c>
+      <c r="C74" s="4">
+        <f t="shared" si="3"/>
+        <v>0.28571428571428559</v>
+      </c>
       <c r="D74" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.27990117734204678</v>
       </c>
       <c r="E74" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.15224729145666602</v>
       </c>
       <c r="F74" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.15108705979319481</v>
       </c>
       <c r="G74" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.4296954177267837E-2</v>
       </c>
       <c r="H74" s="4">
         <v>15</v>
       </c>
       <c r="I74" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>52</v>
       </c>
       <c r="J74" s="4">
-        <f t="shared" si="7"/>
-        <v>8.9172080860896372</v>
+        <f t="shared" si="8"/>
+        <v>8.5742385443169589</v>
       </c>
       <c r="K74" s="4">
-        <f t="shared" si="11"/>
-        <v>35.668832344358549</v>
+        <f t="shared" si="12"/>
+        <v>34.296954177267835</v>
       </c>
       <c r="L74" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M74" s="3">
-        <f>100*$B$12*K74/L74</f>
-        <v>1.188961078145285E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4911719207507753E-2</v>
       </c>
       <c r="N74" s="3">
-        <f t="shared" si="8"/>
-        <v>1.188961078145285E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.4911719207507753E-2</v>
       </c>
     </row>
     <row r="75" spans="1:14">
       <c r="A75" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.6000000000000019</v>
       </c>
       <c r="B75" s="13">
-        <f t="shared" si="1"/>
-        <v>0.27777777777777762</v>
-      </c>
-      <c r="C75" s="4">
         <f t="shared" si="2"/>
         <v>0.27777777777777762</v>
       </c>
+      <c r="C75" s="4">
+        <f t="shared" si="3"/>
+        <v>0.27777777777777762</v>
+      </c>
       <c r="D75" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.26669279140144236</v>
       </c>
       <c r="E75" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.14438015151456501</v>
       </c>
       <c r="F75" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.14338928380567537</v>
       </c>
       <c r="G75" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.263329467129758E-2</v>
       </c>
       <c r="H75" s="4">
         <v>15</v>
       </c>
       <c r="I75" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>53.5</v>
       </c>
       <c r="J75" s="4">
-        <f t="shared" si="7"/>
-        <v>8.4846566145373714</v>
+        <f t="shared" si="8"/>
+        <v>8.1583236678243942</v>
       </c>
       <c r="K75" s="4">
-        <f t="shared" si="11"/>
-        <v>33.938626458149486</v>
+        <f t="shared" si="12"/>
+        <v>32.633294671297577</v>
       </c>
       <c r="L75" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M75" s="3">
-        <f>100*$B$12*K75/L75</f>
-        <v>1.1312875486049829E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.4188388987520685E-2</v>
       </c>
       <c r="N75" s="3">
-        <f t="shared" si="8"/>
-        <v>1.1312875486049829E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.4188388987520685E-2</v>
       </c>
     </row>
     <row r="76" spans="1:14">
       <c r="A76" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.700000000000002</v>
       </c>
       <c r="B76" s="13">
-        <f t="shared" si="1"/>
-        <v>0.27027027027027012</v>
-      </c>
-      <c r="C76" s="4">
         <f t="shared" si="2"/>
         <v>0.27027027027027012</v>
       </c>
+      <c r="C76" s="4">
+        <f t="shared" si="3"/>
+        <v>0.27027027027027012</v>
+      </c>
       <c r="D76" s="3">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>0.25434807074353505</v>
       </c>
       <c r="E76" s="14">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>0.13710188087668926</v>
       </c>
       <c r="F76" s="4">
-        <f t="shared" si="5"/>
+        <f t="shared" si="6"/>
         <v>0.13625240966824725</v>
       </c>
       <c r="G76" s="4">
-        <f t="shared" si="6"/>
+        <f t="shared" si="7"/>
         <v>3.1082998615802097E-2</v>
       </c>
       <c r="H76" s="4">
         <v>15</v>
       </c>
       <c r="I76" s="4">
-        <f t="shared" si="10"/>
+        <f t="shared" si="11"/>
         <v>55</v>
       </c>
       <c r="J76" s="4">
-        <f t="shared" si="7"/>
-        <v>8.0815796401085453</v>
+        <f t="shared" si="8"/>
+        <v>7.7707496539505243</v>
       </c>
       <c r="K76" s="4">
-        <f t="shared" si="11"/>
-        <v>32.326318560434181</v>
+        <f t="shared" si="12"/>
+        <v>31.082998615802097</v>
       </c>
       <c r="L76" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M76" s="3">
-        <f>100*$B$12*K76/L76</f>
-        <v>1.0775439520144727E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.3514347224261782E-2</v>
       </c>
       <c r="N76" s="3">
-        <f t="shared" si="8"/>
-        <v>1.0775439520144727E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.3514347224261782E-2</v>
       </c>
     </row>
     <row r="77" spans="1:14">
       <c r="A77" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.800000000000002</v>
       </c>
       <c r="B77" s="13">
-        <f t="shared" ref="B77:B94" si="12">$B$10/A77</f>
+        <f t="shared" ref="B77:B94" si="14">$B$10/A77</f>
         <v>0.26315789473684198</v>
       </c>
       <c r="C77" s="4">
-        <f t="shared" ref="C77:C94" si="13">$B$9/A77</f>
+        <f t="shared" ref="C77:C94" si="15">$B$9/A77</f>
         <v>0.26315789473684198</v>
       </c>
       <c r="D77" s="3">
-        <f t="shared" ref="D77:D94" si="14">2*C77*B77*SQRT(B77^2+C77^2+1)*(B77^2+C77^2+2)/((C77^2+B77^2+B77^2*C77^2+1)*(C77^2+B77^2+1))</f>
+        <f t="shared" ref="D77:D94" si="16">2*C77*B77*SQRT(B77^2+C77^2+1)*(B77^2+C77^2+2)/((C77^2+B77^2+B77^2*C77^2+1)*(C77^2+B77^2+1))</f>
         <v>0.2427981567272747</v>
       </c>
       <c r="E77" s="14">
-        <f t="shared" ref="E77:E94" si="15">((2*B77*C77*SQRT(B77^2+C77^2+1)/(B77^2+C77^2-C77^2 *B77^2+1)))</f>
+        <f t="shared" ref="E77:E94" si="17">((2*B77*C77*SQRT(B77^2+C77^2+1)/(B77^2+C77^2-C77^2 *B77^2+1)))</f>
         <v>0.1303553272919579</v>
       </c>
       <c r="F77" s="4">
-        <f t="shared" ref="F77:F94" si="16">IF(E77&lt;0,ATAN(E77)+PI(),ATAN(E77))</f>
+        <f t="shared" ref="F77:F94" si="18">IF(E77&lt;0,ATAN(E77)+PI(),ATAN(E77))</f>
         <v>0.12962441022135229</v>
       </c>
       <c r="G77" s="4">
-        <f t="shared" ref="G77:G94" si="17">(D77+F77)/(4*PI())</f>
+        <f t="shared" ref="G77:G94" si="19">(D77+F77)/(4*PI())</f>
         <v>2.9636446224423154E-2</v>
       </c>
       <c r="H77" s="4">
         <v>15</v>
       </c>
       <c r="I77" s="4">
-        <f t="shared" ref="I77:I94" si="18">I76+(A77-A76)*H77</f>
+        <f t="shared" ref="I77:I94" si="20">I76+(A77-A76)*H77</f>
         <v>56.5</v>
       </c>
       <c r="J77" s="4">
-        <f t="shared" ref="J77:J94" si="19">G77*$B$14</f>
-        <v>7.7054760183500202</v>
+        <f t="shared" ref="J77:J94" si="21">G77*$B$14</f>
+        <v>7.4091115561057883</v>
       </c>
       <c r="K77" s="4">
-        <f t="shared" si="11"/>
-        <v>30.821904073400081</v>
+        <f t="shared" si="12"/>
+        <v>29.636446224423153</v>
       </c>
       <c r="L77" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M77" s="3">
-        <f>100*$B$12*K77/L77</f>
-        <v>1.0273968024466694E-2</v>
+        <f t="shared" si="13"/>
+        <v>1.2885411401923109E-2</v>
       </c>
       <c r="N77" s="3">
-        <f t="shared" si="8"/>
-        <v>1.0273968024466694E-2</v>
+        <f t="shared" si="9"/>
+        <v>1.2885411401923109E-2</v>
       </c>
     </row>
     <row r="78" spans="1:14">
       <c r="A78" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>3.9000000000000021</v>
       </c>
       <c r="B78" s="13">
+        <f t="shared" si="14"/>
+        <v>0.25641025641025628</v>
+      </c>
+      <c r="C78" s="4">
+        <f t="shared" si="15"/>
+        <v>0.25641025641025628</v>
+      </c>
+      <c r="D78" s="3">
+        <f t="shared" si="16"/>
+        <v>0.2319803227597026</v>
+      </c>
+      <c r="E78" s="14">
+        <f t="shared" si="17"/>
+        <v>0.12409012927699317</v>
+      </c>
+      <c r="F78" s="4">
+        <f t="shared" si="18"/>
+        <v>0.12345902173990503</v>
+      </c>
+      <c r="G78" s="4">
+        <f t="shared" si="19"/>
+        <v>2.8284964323227819E-2</v>
+      </c>
+      <c r="H78" s="4">
+        <v>15</v>
+      </c>
+      <c r="I78" s="4">
+        <f t="shared" si="20"/>
+        <v>58</v>
+      </c>
+      <c r="J78" s="4">
+        <f t="shared" si="21"/>
+        <v>7.0712410808069546</v>
+      </c>
+      <c r="K78" s="4">
         <f t="shared" si="12"/>
-        <v>0.25641025641025628</v>
-      </c>
-      <c r="C78" s="4">
+        <v>28.284964323227818</v>
+      </c>
+      <c r="L78" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M78" s="3">
         <f t="shared" si="13"/>
-        <v>0.25641025641025628</v>
-      </c>
-      <c r="D78" s="3">
-        <f t="shared" si="14"/>
-        <v>0.2319803227597026</v>
-      </c>
-      <c r="E78" s="14">
-        <f t="shared" si="15"/>
-        <v>0.12409012927699317</v>
-      </c>
-      <c r="F78" s="4">
-        <f t="shared" si="16"/>
-        <v>0.12345902173990503</v>
-      </c>
-      <c r="G78" s="4">
-        <f t="shared" si="17"/>
-        <v>2.8284964323227819E-2</v>
-      </c>
-      <c r="H78" s="4">
-        <v>15</v>
-      </c>
-      <c r="I78" s="4">
-        <f t="shared" si="18"/>
-        <v>58</v>
-      </c>
-      <c r="J78" s="4">
-        <f t="shared" si="19"/>
-        <v>7.3540907240392333</v>
-      </c>
-      <c r="K78" s="4">
-        <f t="shared" si="11"/>
-        <v>29.416362896156933</v>
-      </c>
-      <c r="L78" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M78" s="3">
-        <f>100*$B$12*K78/L78</f>
-        <v>9.8054542987189765E-3</v>
+        <v>1.2297810575316443E-2</v>
       </c>
       <c r="N78" s="3">
-        <f t="shared" si="8"/>
-        <v>9.8054542987189765E-3</v>
+        <f t="shared" si="9"/>
+        <v>1.2297810575316443E-2</v>
       </c>
     </row>
     <row r="79" spans="1:14">
       <c r="A79" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.0000000000000018</v>
       </c>
       <c r="B79" s="13">
+        <f t="shared" si="14"/>
+        <v>0.24999999999999989</v>
+      </c>
+      <c r="C79" s="4">
+        <f t="shared" si="15"/>
+        <v>0.24999999999999989</v>
+      </c>
+      <c r="D79" s="3">
+        <f t="shared" si="16"/>
+        <v>0.22183742154872058</v>
+      </c>
+      <c r="E79" s="14">
+        <f t="shared" si="17"/>
+        <v>0.11826176131342944</v>
+      </c>
+      <c r="F79" s="4">
+        <f t="shared" si="18"/>
+        <v>0.11771501189416235</v>
+      </c>
+      <c r="G79" s="4">
+        <f t="shared" si="19"/>
+        <v>2.7020724110658308E-2</v>
+      </c>
+      <c r="H79" s="4">
+        <v>15</v>
+      </c>
+      <c r="I79" s="4">
+        <f t="shared" si="20"/>
+        <v>59.499999999999993</v>
+      </c>
+      <c r="J79" s="4">
+        <f t="shared" si="21"/>
+        <v>6.7551810276645767</v>
+      </c>
+      <c r="K79" s="4">
         <f t="shared" si="12"/>
-        <v>0.24999999999999989</v>
-      </c>
-      <c r="C79" s="4">
+        <v>27.020724110658307</v>
+      </c>
+      <c r="L79" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M79" s="3">
         <f t="shared" si="13"/>
-        <v>0.24999999999999989</v>
-      </c>
-      <c r="D79" s="3">
-        <f t="shared" si="14"/>
-        <v>0.22183742154872058</v>
-      </c>
-      <c r="E79" s="14">
-        <f t="shared" si="15"/>
-        <v>0.11826176131342944</v>
-      </c>
-      <c r="F79" s="4">
-        <f t="shared" si="16"/>
-        <v>0.11771501189416235</v>
-      </c>
-      <c r="G79" s="4">
-        <f t="shared" si="17"/>
-        <v>2.7020724110658308E-2</v>
-      </c>
-      <c r="H79" s="4">
-        <v>15</v>
-      </c>
-      <c r="I79" s="4">
-        <f t="shared" si="18"/>
-        <v>59.499999999999993</v>
-      </c>
-      <c r="J79" s="4">
-        <f t="shared" si="19"/>
-        <v>7.0253882687711604</v>
-      </c>
-      <c r="K79" s="4">
-        <f t="shared" si="11"/>
-        <v>28.101553075084642</v>
-      </c>
-      <c r="L79" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M79" s="3">
-        <f>100*$B$12*K79/L79</f>
-        <v>9.3671843583615477E-3</v>
+        <v>1.1748140917677525E-2</v>
       </c>
       <c r="N79" s="3">
-        <f t="shared" si="8"/>
-        <v>9.3671843583615477E-3</v>
+        <f t="shared" si="9"/>
+        <v>1.1748140917677525E-2</v>
       </c>
     </row>
     <row r="80" spans="1:14">
       <c r="A80" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.1000000000000014</v>
       </c>
       <c r="B80" s="13">
+        <f t="shared" si="14"/>
+        <v>0.24390243902439016</v>
+      </c>
+      <c r="C80" s="4">
+        <f t="shared" si="15"/>
+        <v>0.24390243902439016</v>
+      </c>
+      <c r="D80" s="3">
+        <f t="shared" si="16"/>
+        <v>0.21231737240134041</v>
+      </c>
+      <c r="E80" s="14">
+        <f t="shared" si="17"/>
+        <v>0.11283073440696234</v>
+      </c>
+      <c r="F80" s="4">
+        <f t="shared" si="18"/>
+        <v>0.112355551279421</v>
+      </c>
+      <c r="G80" s="4">
+        <f t="shared" si="19"/>
+        <v>2.5836650345945431E-2</v>
+      </c>
+      <c r="H80" s="4">
+        <v>15</v>
+      </c>
+      <c r="I80" s="4">
+        <f t="shared" si="20"/>
+        <v>60.999999999999986</v>
+      </c>
+      <c r="J80" s="4">
+        <f t="shared" si="21"/>
+        <v>6.4591625864863582</v>
+      </c>
+      <c r="K80" s="4">
         <f t="shared" si="12"/>
-        <v>0.24390243902439016</v>
-      </c>
-      <c r="C80" s="4">
+        <v>25.836650345945433</v>
+      </c>
+      <c r="L80" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M80" s="3">
         <f t="shared" si="13"/>
-        <v>0.24390243902439016</v>
-      </c>
-      <c r="D80" s="3">
-        <f t="shared" si="14"/>
-        <v>0.21231737240134041</v>
-      </c>
-      <c r="E80" s="14">
-        <f t="shared" si="15"/>
-        <v>0.11283073440696234</v>
-      </c>
-      <c r="F80" s="4">
-        <f t="shared" si="16"/>
-        <v>0.112355551279421</v>
-      </c>
-      <c r="G80" s="4">
-        <f t="shared" si="17"/>
-        <v>2.5836650345945431E-2</v>
-      </c>
-      <c r="H80" s="4">
-        <v>15</v>
-      </c>
-      <c r="I80" s="4">
-        <f t="shared" si="18"/>
-        <v>60.999999999999986</v>
-      </c>
-      <c r="J80" s="4">
-        <f t="shared" si="19"/>
-        <v>6.7175290899458124</v>
-      </c>
-      <c r="K80" s="4">
-        <f t="shared" si="11"/>
-        <v>26.87011635978325</v>
-      </c>
-      <c r="L80" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M80" s="3">
-        <f>100*$B$12*K80/L80</f>
-        <v>8.956705453261082E-3</v>
+        <v>1.1233326237367581E-2</v>
       </c>
       <c r="N80" s="3">
-        <f t="shared" si="8"/>
-        <v>8.956705453261082E-3</v>
+        <f t="shared" si="9"/>
+        <v>1.1233326237367581E-2</v>
       </c>
     </row>
     <row r="81" spans="1:14">
       <c r="A81" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.2000000000000011</v>
       </c>
       <c r="B81" s="13">
+        <f t="shared" si="14"/>
+        <v>0.23809523809523803</v>
+      </c>
+      <c r="C81" s="4">
+        <f t="shared" si="15"/>
+        <v>0.23809523809523803</v>
+      </c>
+      <c r="D81" s="3">
+        <f t="shared" si="16"/>
+        <v>0.2033726894965022</v>
+      </c>
+      <c r="E81" s="14">
+        <f t="shared" si="17"/>
+        <v>0.10776192322801748</v>
+      </c>
+      <c r="F81" s="4">
+        <f t="shared" si="18"/>
+        <v>0.10734767255484386</v>
+      </c>
+      <c r="G81" s="4">
+        <f t="shared" si="19"/>
+        <v>2.4726340769887549E-2</v>
+      </c>
+      <c r="H81" s="4">
+        <v>15</v>
+      </c>
+      <c r="I81" s="4">
+        <f t="shared" si="20"/>
+        <v>62.499999999999979</v>
+      </c>
+      <c r="J81" s="4">
+        <f t="shared" si="21"/>
+        <v>6.1815851924718874</v>
+      </c>
+      <c r="K81" s="4">
         <f t="shared" si="12"/>
-        <v>0.23809523809523803</v>
-      </c>
-      <c r="C81" s="4">
+        <v>24.72634076988755</v>
+      </c>
+      <c r="L81" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M81" s="3">
         <f t="shared" si="13"/>
-        <v>0.23809523809523803</v>
-      </c>
-      <c r="D81" s="3">
-        <f t="shared" si="14"/>
-        <v>0.2033726894965022</v>
-      </c>
-      <c r="E81" s="14">
-        <f t="shared" si="15"/>
-        <v>0.10776192322801748</v>
-      </c>
-      <c r="F81" s="4">
-        <f t="shared" si="16"/>
-        <v>0.10734767255484386</v>
-      </c>
-      <c r="G81" s="4">
-        <f t="shared" si="17"/>
-        <v>2.4726340769887549E-2</v>
-      </c>
-      <c r="H81" s="4">
-        <v>15</v>
-      </c>
-      <c r="I81" s="4">
-        <f t="shared" si="18"/>
-        <v>62.499999999999979</v>
-      </c>
-      <c r="J81" s="4">
-        <f t="shared" si="19"/>
-        <v>6.4288486001707623</v>
-      </c>
-      <c r="K81" s="4">
-        <f t="shared" si="11"/>
-        <v>25.715394400683049</v>
-      </c>
-      <c r="L81" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M81" s="3">
-        <f>100*$B$12*K81/L81</f>
-        <v>8.5717981335610167E-3</v>
+        <v>1.0750582943429369E-2</v>
       </c>
       <c r="N81" s="3">
-        <f t="shared" si="8"/>
-        <v>8.5717981335610167E-3</v>
+        <f t="shared" si="9"/>
+        <v>1.0750582943429369E-2</v>
       </c>
     </row>
     <row r="82" spans="1:14">
       <c r="A82" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.3000000000000007</v>
       </c>
       <c r="B82" s="13">
+        <f t="shared" si="14"/>
+        <v>0.23255813953488369</v>
+      </c>
+      <c r="C82" s="4">
+        <f t="shared" si="15"/>
+        <v>0.23255813953488369</v>
+      </c>
+      <c r="D82" s="3">
+        <f t="shared" si="16"/>
+        <v>0.19496005046339826</v>
+      </c>
+      <c r="E82" s="14">
+        <f t="shared" si="17"/>
+        <v>0.10302399704091958</v>
+      </c>
+      <c r="F82" s="4">
+        <f t="shared" si="18"/>
+        <v>0.10266180385968492</v>
+      </c>
+      <c r="G82" s="4">
+        <f t="shared" si="19"/>
+        <v>2.3683994643847336E-2</v>
+      </c>
+      <c r="H82" s="4">
+        <v>15</v>
+      </c>
+      <c r="I82" s="4">
+        <f t="shared" si="20"/>
+        <v>63.999999999999972</v>
+      </c>
+      <c r="J82" s="4">
+        <f t="shared" si="21"/>
+        <v>5.9209986609618337</v>
+      </c>
+      <c r="K82" s="4">
         <f t="shared" si="12"/>
-        <v>0.23255813953488369</v>
-      </c>
-      <c r="C82" s="4">
+        <v>23.683994643847335</v>
+      </c>
+      <c r="L82" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M82" s="3">
         <f t="shared" si="13"/>
-        <v>0.23255813953488369</v>
-      </c>
-      <c r="D82" s="3">
-        <f t="shared" si="14"/>
-        <v>0.19496005046339826</v>
-      </c>
-      <c r="E82" s="14">
-        <f t="shared" si="15"/>
-        <v>0.10302399704091958</v>
-      </c>
-      <c r="F82" s="4">
-        <f t="shared" si="16"/>
-        <v>0.10266180385968492</v>
-      </c>
-      <c r="G82" s="4">
-        <f t="shared" si="17"/>
-        <v>2.3683994643847336E-2</v>
-      </c>
-      <c r="H82" s="4">
-        <v>15</v>
-      </c>
-      <c r="I82" s="4">
-        <f t="shared" si="18"/>
-        <v>63.999999999999972</v>
-      </c>
-      <c r="J82" s="4">
-        <f t="shared" si="19"/>
-        <v>6.1578386074003078</v>
-      </c>
-      <c r="K82" s="4">
-        <f t="shared" si="11"/>
-        <v>24.631354429601231</v>
-      </c>
-      <c r="L82" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M82" s="3">
-        <f>100*$B$12*K82/L82</f>
-        <v>8.2104514765337436E-3</v>
+        <v>1.0297388975585799E-2</v>
       </c>
       <c r="N82" s="3">
-        <f t="shared" si="8"/>
-        <v>8.2104514765337436E-3</v>
+        <f t="shared" si="9"/>
+        <v>1.0297388975585799E-2</v>
       </c>
     </row>
     <row r="83" spans="1:14">
       <c r="A83" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.4000000000000004</v>
       </c>
       <c r="B83" s="13">
+        <f t="shared" si="14"/>
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="C83" s="4">
+        <f t="shared" si="15"/>
+        <v>0.22727272727272727</v>
+      </c>
+      <c r="D83" s="3">
+        <f t="shared" si="16"/>
+        <v>0.18703990359477682</v>
+      </c>
+      <c r="E83" s="14">
+        <f t="shared" si="17"/>
+        <v>9.8588936234358771E-2</v>
+      </c>
+      <c r="F83" s="4">
+        <f t="shared" si="18"/>
+        <v>9.8271365349141132E-2</v>
+      </c>
+      <c r="G83" s="4">
+        <f t="shared" si="19"/>
+        <v>2.2704349386122855E-2</v>
+      </c>
+      <c r="H83" s="4">
+        <v>15</v>
+      </c>
+      <c r="I83" s="4">
+        <f t="shared" si="20"/>
+        <v>65.499999999999972</v>
+      </c>
+      <c r="J83" s="4">
+        <f t="shared" si="21"/>
+        <v>5.6760873465307133</v>
+      </c>
+      <c r="K83" s="4">
         <f t="shared" si="12"/>
-        <v>0.22727272727272727</v>
-      </c>
-      <c r="C83" s="4">
+        <v>22.704349386122853</v>
+      </c>
+      <c r="L83" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M83" s="3">
         <f t="shared" si="13"/>
-        <v>0.22727272727272727</v>
-      </c>
-      <c r="D83" s="3">
-        <f t="shared" si="14"/>
-        <v>0.18703990359477682</v>
-      </c>
-      <c r="E83" s="14">
-        <f t="shared" si="15"/>
-        <v>9.8588936234358771E-2</v>
-      </c>
-      <c r="F83" s="4">
-        <f t="shared" si="16"/>
-        <v>9.8271365349141132E-2</v>
-      </c>
-      <c r="G83" s="4">
-        <f t="shared" si="17"/>
-        <v>2.2704349386122855E-2</v>
-      </c>
-      <c r="H83" s="4">
-        <v>15</v>
-      </c>
-      <c r="I83" s="4">
-        <f t="shared" si="18"/>
-        <v>65.499999999999972</v>
-      </c>
-      <c r="J83" s="4">
-        <f t="shared" si="19"/>
-        <v>5.9031308403919418</v>
-      </c>
-      <c r="K83" s="4">
-        <f t="shared" si="11"/>
-        <v>23.612523361567767</v>
-      </c>
-      <c r="L83" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M83" s="3">
-        <f>100*$B$12*K83/L83</f>
-        <v>7.8708411205225884E-3</v>
+        <v>9.8714562548360228E-3</v>
       </c>
       <c r="N83" s="3">
-        <f t="shared" si="8"/>
-        <v>7.8708411205225884E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.8714562548360228E-3</v>
       </c>
     </row>
     <row r="84" spans="1:14">
       <c r="A84" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.5</v>
       </c>
       <c r="B84" s="13">
+        <f t="shared" si="14"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="C84" s="4">
+        <f t="shared" si="15"/>
+        <v>0.22222222222222221</v>
+      </c>
+      <c r="D84" s="3">
+        <f t="shared" si="16"/>
+        <v>0.17957611143637153</v>
+      </c>
+      <c r="E84" s="14">
+        <f t="shared" si="17"/>
+        <v>9.4431619839854777E-2</v>
+      </c>
+      <c r="F84" s="4">
+        <f t="shared" si="18"/>
+        <v>9.415241949263578E-2</v>
+      </c>
+      <c r="G84" s="4">
+        <f t="shared" si="19"/>
+        <v>2.1782624381317135E-2</v>
+      </c>
+      <c r="H84" s="4">
+        <v>15</v>
+      </c>
+      <c r="I84" s="4">
+        <f t="shared" si="20"/>
+        <v>66.999999999999972</v>
+      </c>
+      <c r="J84" s="4">
+        <f t="shared" si="21"/>
+        <v>5.4456560953292836</v>
+      </c>
+      <c r="K84" s="4">
         <f t="shared" si="12"/>
-        <v>0.22222222222222221</v>
-      </c>
-      <c r="C84" s="4">
+        <v>21.782624381317135</v>
+      </c>
+      <c r="L84" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M84" s="3">
         <f t="shared" si="13"/>
-        <v>0.22222222222222221</v>
-      </c>
-      <c r="D84" s="3">
-        <f t="shared" si="14"/>
-        <v>0.17957611143637153</v>
-      </c>
-      <c r="E84" s="14">
-        <f t="shared" si="15"/>
-        <v>9.4431619839854777E-2</v>
-      </c>
-      <c r="F84" s="4">
-        <f t="shared" si="16"/>
-        <v>9.415241949263578E-2</v>
-      </c>
-      <c r="G84" s="4">
-        <f t="shared" si="17"/>
-        <v>2.1782624381317135E-2</v>
-      </c>
-      <c r="H84" s="4">
-        <v>15</v>
-      </c>
-      <c r="I84" s="4">
-        <f t="shared" si="18"/>
-        <v>66.999999999999972</v>
-      </c>
-      <c r="J84" s="4">
-        <f t="shared" si="19"/>
-        <v>5.6634823391424547</v>
-      </c>
-      <c r="K84" s="4">
-        <f t="shared" si="11"/>
-        <v>22.653929356569819</v>
-      </c>
-      <c r="L84" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M84" s="3">
-        <f>100*$B$12*K84/L84</f>
-        <v>7.5513097855232731E-3</v>
+        <v>9.4707062527465795E-3</v>
       </c>
       <c r="N84" s="3">
-        <f t="shared" si="8"/>
-        <v>7.5513097855232731E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.4707062527465795E-3</v>
       </c>
     </row>
     <row r="85" spans="1:14">
       <c r="A85" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.5999999999999996</v>
       </c>
       <c r="B85" s="13">
+        <f t="shared" si="14"/>
+        <v>0.21739130434782611</v>
+      </c>
+      <c r="C85" s="4">
+        <f t="shared" si="15"/>
+        <v>0.21739130434782611</v>
+      </c>
+      <c r="D85" s="3">
+        <f t="shared" si="16"/>
+        <v>0.17253562818806684</v>
+      </c>
+      <c r="E85" s="14">
+        <f t="shared" si="17"/>
+        <v>9.0529472220288565E-2</v>
+      </c>
+      <c r="F85" s="4">
+        <f t="shared" si="18"/>
+        <v>9.0283367270839646E-2</v>
+      </c>
+      <c r="G85" s="4">
+        <f t="shared" si="19"/>
+        <v>2.0914471132865681E-2</v>
+      </c>
+      <c r="H85" s="4">
+        <v>15</v>
+      </c>
+      <c r="I85" s="4">
+        <f t="shared" si="20"/>
+        <v>68.499999999999972</v>
+      </c>
+      <c r="J85" s="4">
+        <f t="shared" si="21"/>
+        <v>5.2286177832164205</v>
+      </c>
+      <c r="K85" s="4">
         <f t="shared" si="12"/>
-        <v>0.21739130434782611</v>
-      </c>
-      <c r="C85" s="4">
+        <v>20.914471132865682</v>
+      </c>
+      <c r="L85" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M85" s="3">
         <f t="shared" si="13"/>
-        <v>0.21739130434782611</v>
-      </c>
-      <c r="D85" s="3">
-        <f t="shared" si="14"/>
-        <v>0.17253562818806684</v>
-      </c>
-      <c r="E85" s="14">
-        <f t="shared" si="15"/>
-        <v>9.0529472220288565E-2</v>
-      </c>
-      <c r="F85" s="4">
-        <f t="shared" si="16"/>
-        <v>9.0283367270839646E-2</v>
-      </c>
-      <c r="G85" s="4">
-        <f t="shared" si="17"/>
-        <v>2.0914471132865681E-2</v>
-      </c>
-      <c r="H85" s="4">
-        <v>15</v>
-      </c>
-      <c r="I85" s="4">
-        <f t="shared" si="18"/>
-        <v>68.499999999999972</v>
-      </c>
-      <c r="J85" s="4">
-        <f t="shared" si="19"/>
-        <v>5.4377624945450771</v>
-      </c>
-      <c r="K85" s="4">
-        <f t="shared" si="11"/>
-        <v>21.751049978180308</v>
-      </c>
-      <c r="L85" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M85" s="3">
-        <f>100*$B$12*K85/L85</f>
-        <v>7.2503499927267694E-3</v>
+        <v>9.0932483186372537E-3</v>
       </c>
       <c r="N85" s="3">
-        <f t="shared" si="8"/>
-        <v>7.2503499927267694E-3</v>
+        <f t="shared" si="9"/>
+        <v>9.0932483186372537E-3</v>
       </c>
     </row>
     <row r="86" spans="1:14">
       <c r="A86" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.6999999999999993</v>
       </c>
       <c r="B86" s="13">
+        <f t="shared" si="14"/>
+        <v>0.21276595744680854</v>
+      </c>
+      <c r="C86" s="4">
+        <f t="shared" si="15"/>
+        <v>0.21276595744680854</v>
+      </c>
+      <c r="D86" s="3">
+        <f t="shared" si="16"/>
+        <v>0.16588820823743711</v>
+      </c>
+      <c r="E86" s="14">
+        <f t="shared" si="17"/>
+        <v>8.686215931337829E-2</v>
+      </c>
+      <c r="F86" s="4">
+        <f t="shared" si="18"/>
+        <v>8.6644683648588017E-2</v>
+      </c>
+      <c r="G86" s="4">
+        <f t="shared" si="19"/>
+        <v>2.0095929018476042E-2</v>
+      </c>
+      <c r="H86" s="4">
+        <v>15</v>
+      </c>
+      <c r="I86" s="4">
+        <f t="shared" si="20"/>
+        <v>69.999999999999972</v>
+      </c>
+      <c r="J86" s="4">
+        <f t="shared" si="21"/>
+        <v>5.0239822546190105</v>
+      </c>
+      <c r="K86" s="4">
         <f t="shared" si="12"/>
-        <v>0.21276595744680854</v>
-      </c>
-      <c r="C86" s="4">
+        <v>20.095929018476042</v>
+      </c>
+      <c r="L86" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M86" s="3">
         <f t="shared" si="13"/>
-        <v>0.21276595744680854</v>
-      </c>
-      <c r="D86" s="3">
-        <f t="shared" si="14"/>
-        <v>0.16588820823743711</v>
-      </c>
-      <c r="E86" s="14">
-        <f t="shared" si="15"/>
-        <v>8.686215931337829E-2</v>
-      </c>
-      <c r="F86" s="4">
-        <f t="shared" si="16"/>
-        <v>8.6644683648588017E-2</v>
-      </c>
-      <c r="G86" s="4">
-        <f t="shared" si="17"/>
-        <v>2.0095929018476042E-2</v>
-      </c>
-      <c r="H86" s="4">
-        <v>15</v>
-      </c>
-      <c r="I86" s="4">
-        <f t="shared" si="18"/>
-        <v>69.999999999999972</v>
-      </c>
-      <c r="J86" s="4">
-        <f t="shared" si="19"/>
-        <v>5.2249415448037713</v>
-      </c>
-      <c r="K86" s="4">
-        <f t="shared" si="11"/>
-        <v>20.899766179215085</v>
-      </c>
-      <c r="L86" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M86" s="3">
-        <f>100*$B$12*K86/L86</f>
-        <v>6.9665887264050283E-3</v>
+        <v>8.7373604428156709E-3</v>
       </c>
       <c r="N86" s="3">
-        <f t="shared" si="8"/>
-        <v>6.9665887264050283E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.7373604428156709E-3</v>
       </c>
     </row>
     <row r="87" spans="1:14">
       <c r="A87" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.7999999999999989</v>
       </c>
       <c r="B87" s="13">
+        <f t="shared" si="14"/>
+        <v>0.20833333333333337</v>
+      </c>
+      <c r="C87" s="4">
+        <f t="shared" si="15"/>
+        <v>0.20833333333333337</v>
+      </c>
+      <c r="D87" s="3">
+        <f t="shared" si="16"/>
+        <v>0.15960614315689151</v>
+      </c>
+      <c r="E87" s="14">
+        <f t="shared" si="17"/>
+        <v>8.3411326562983112E-2</v>
+      </c>
+      <c r="F87" s="4">
+        <f t="shared" si="18"/>
+        <v>8.3218686733652722E-2</v>
+      </c>
+      <c r="G87" s="4">
+        <f t="shared" si="19"/>
+        <v>1.9323385991264364E-2</v>
+      </c>
+      <c r="H87" s="4">
+        <v>15</v>
+      </c>
+      <c r="I87" s="4">
+        <f t="shared" si="20"/>
+        <v>71.499999999999972</v>
+      </c>
+      <c r="J87" s="4">
+        <f t="shared" si="21"/>
+        <v>4.8308464978160908</v>
+      </c>
+      <c r="K87" s="4">
         <f t="shared" si="12"/>
-        <v>0.20833333333333337</v>
-      </c>
-      <c r="C87" s="4">
+        <v>19.323385991264363</v>
+      </c>
+      <c r="L87" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M87" s="3">
         <f t="shared" si="13"/>
-        <v>0.20833333333333337</v>
-      </c>
-      <c r="D87" s="3">
-        <f t="shared" si="14"/>
-        <v>0.15960614315689151</v>
-      </c>
-      <c r="E87" s="14">
-        <f t="shared" si="15"/>
-        <v>8.3411326562983112E-2</v>
-      </c>
-      <c r="F87" s="4">
-        <f t="shared" si="16"/>
-        <v>8.3218686733652722E-2</v>
-      </c>
-      <c r="G87" s="4">
-        <f t="shared" si="17"/>
-        <v>1.9323385991264364E-2</v>
-      </c>
-      <c r="H87" s="4">
-        <v>15</v>
-      </c>
-      <c r="I87" s="4">
-        <f t="shared" si="18"/>
-        <v>71.499999999999972</v>
-      </c>
-      <c r="J87" s="4">
-        <f t="shared" si="19"/>
-        <v>5.0240803577287343</v>
-      </c>
-      <c r="K87" s="4">
-        <f t="shared" si="11"/>
-        <v>20.096321430914937</v>
-      </c>
-      <c r="L87" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M87" s="3">
-        <f>100*$B$12*K87/L87</f>
-        <v>6.6987738103049792E-3</v>
+        <v>8.4014721701149396E-3</v>
       </c>
       <c r="N87" s="3">
-        <f t="shared" si="8"/>
-        <v>6.6987738103049792E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.4014721701149396E-3</v>
       </c>
     </row>
     <row r="88" spans="1:14">
       <c r="A88" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.8999999999999986</v>
       </c>
       <c r="B88" s="13">
+        <f t="shared" si="14"/>
+        <v>0.20408163265306128</v>
+      </c>
+      <c r="C88" s="4">
+        <f t="shared" si="15"/>
+        <v>0.20408163265306128</v>
+      </c>
+      <c r="D88" s="3">
+        <f t="shared" si="16"/>
+        <v>0.15366402458624401</v>
+      </c>
+      <c r="E88" s="14">
+        <f t="shared" si="17"/>
+        <v>8.0160372067302033E-2</v>
+      </c>
+      <c r="F88" s="4">
+        <f t="shared" si="18"/>
+        <v>7.9989335892602167E-2</v>
+      </c>
+      <c r="G88" s="4">
+        <f t="shared" si="19"/>
+        <v>1.8593543645120433E-2</v>
+      </c>
+      <c r="H88" s="4">
+        <v>15</v>
+      </c>
+      <c r="I88" s="4">
+        <f t="shared" si="20"/>
+        <v>72.999999999999972</v>
+      </c>
+      <c r="J88" s="4">
+        <f t="shared" si="21"/>
+        <v>4.6483859112801085</v>
+      </c>
+      <c r="K88" s="4">
         <f t="shared" si="12"/>
-        <v>0.20408163265306128</v>
-      </c>
-      <c r="C88" s="4">
+        <v>18.593543645120434</v>
+      </c>
+      <c r="L88" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M88" s="3">
         <f t="shared" si="13"/>
-        <v>0.20408163265306128</v>
-      </c>
-      <c r="D88" s="3">
-        <f t="shared" si="14"/>
-        <v>0.15366402458624401</v>
-      </c>
-      <c r="E88" s="14">
-        <f t="shared" si="15"/>
-        <v>8.0160372067302033E-2</v>
-      </c>
-      <c r="F88" s="4">
-        <f t="shared" si="16"/>
-        <v>7.9989335892602167E-2</v>
-      </c>
-      <c r="G88" s="4">
-        <f t="shared" si="17"/>
-        <v>1.8593543645120433E-2</v>
-      </c>
-      <c r="H88" s="4">
-        <v>15</v>
-      </c>
-      <c r="I88" s="4">
-        <f t="shared" si="18"/>
-        <v>72.999999999999972</v>
-      </c>
-      <c r="J88" s="4">
-        <f t="shared" si="19"/>
-        <v>4.8343213477313123</v>
-      </c>
-      <c r="K88" s="4">
-        <f t="shared" si="11"/>
-        <v>19.337285390925249</v>
-      </c>
-      <c r="L88" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M88" s="3">
-        <f>100*$B$12*K88/L88</f>
-        <v>6.4457617969750827E-3</v>
+        <v>8.0841494109219272E-3</v>
       </c>
       <c r="N88" s="3">
-        <f t="shared" si="8"/>
-        <v>6.4457617969750827E-3</v>
+        <f t="shared" si="9"/>
+        <v>8.0841494109219272E-3</v>
       </c>
     </row>
     <row r="89" spans="1:14">
       <c r="A89" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>4.9999999999999982</v>
       </c>
       <c r="B89" s="13">
+        <f t="shared" si="14"/>
+        <v>0.20000000000000007</v>
+      </c>
+      <c r="C89" s="4">
+        <f t="shared" si="15"/>
+        <v>0.20000000000000007</v>
+      </c>
+      <c r="D89" s="3">
+        <f t="shared" si="16"/>
+        <v>0.14803853056144259</v>
+      </c>
+      <c r="E89" s="14">
+        <f t="shared" si="17"/>
+        <v>7.709424959505394E-2</v>
+      </c>
+      <c r="F89" s="4">
+        <f t="shared" si="18"/>
+        <v>7.6942054814656699E-2</v>
+      </c>
+      <c r="G89" s="4">
+        <f t="shared" si="19"/>
+        <v>1.790338613115719E-2</v>
+      </c>
+      <c r="H89" s="4">
+        <v>15</v>
+      </c>
+      <c r="I89" s="4">
+        <f t="shared" si="20"/>
+        <v>74.499999999999972</v>
+      </c>
+      <c r="J89" s="4">
+        <f t="shared" si="21"/>
+        <v>4.4758465327892978</v>
+      </c>
+      <c r="K89" s="4">
         <f t="shared" si="12"/>
-        <v>0.20000000000000007</v>
-      </c>
-      <c r="C89" s="4">
+        <v>17.903386131157191</v>
+      </c>
+      <c r="L89" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M89" s="3">
         <f t="shared" si="13"/>
-        <v>0.20000000000000007</v>
-      </c>
-      <c r="D89" s="3">
-        <f t="shared" si="14"/>
-        <v>0.14803853056144259</v>
-      </c>
-      <c r="E89" s="14">
-        <f t="shared" si="15"/>
-        <v>7.709424959505394E-2</v>
-      </c>
-      <c r="F89" s="4">
-        <f t="shared" si="16"/>
-        <v>7.6942054814656699E-2</v>
-      </c>
-      <c r="G89" s="4">
-        <f t="shared" si="17"/>
-        <v>1.790338613115719E-2</v>
-      </c>
-      <c r="H89" s="4">
-        <v>15</v>
-      </c>
-      <c r="I89" s="4">
-        <f t="shared" si="18"/>
-        <v>74.499999999999972</v>
-      </c>
-      <c r="J89" s="4">
-        <f t="shared" si="19"/>
-        <v>4.6548803941008696</v>
-      </c>
-      <c r="K89" s="4">
-        <f t="shared" si="11"/>
-        <v>18.619521576403478</v>
-      </c>
-      <c r="L89" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M89" s="3">
-        <f>100*$B$12*K89/L89</f>
-        <v>6.2065071921344932E-3</v>
+        <v>7.784080926590083E-3</v>
       </c>
       <c r="N89" s="3">
-        <f t="shared" si="8"/>
-        <v>6.2065071921344932E-3</v>
+        <f t="shared" si="9"/>
+        <v>7.784080926590083E-3</v>
       </c>
     </row>
     <row r="90" spans="1:14">
       <c r="A90" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.0999999999999979</v>
       </c>
       <c r="B90" s="13">
+        <f t="shared" si="14"/>
+        <v>0.1960784313725491</v>
+      </c>
+      <c r="C90" s="4">
+        <f t="shared" si="15"/>
+        <v>0.1960784313725491</v>
+      </c>
+      <c r="D90" s="3">
+        <f t="shared" si="16"/>
+        <v>0.14270823301560323</v>
+      </c>
+      <c r="E90" s="14">
+        <f t="shared" si="17"/>
+        <v>7.4199297027598837E-2</v>
+      </c>
+      <c r="F90" s="4">
+        <f t="shared" si="18"/>
+        <v>7.4063576117031238E-2</v>
+      </c>
+      <c r="G90" s="4">
+        <f t="shared" si="19"/>
+        <v>1.7250152473215818E-2</v>
+      </c>
+      <c r="H90" s="4">
+        <v>15</v>
+      </c>
+      <c r="I90" s="4">
+        <f t="shared" si="20"/>
+        <v>75.999999999999972</v>
+      </c>
+      <c r="J90" s="4">
+        <f t="shared" si="21"/>
+        <v>4.3125381183039551</v>
+      </c>
+      <c r="K90" s="4">
         <f t="shared" si="12"/>
-        <v>0.1960784313725491</v>
-      </c>
-      <c r="C90" s="4">
+        <v>17.25015247321582</v>
+      </c>
+      <c r="L90" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M90" s="3">
         <f t="shared" si="13"/>
-        <v>0.1960784313725491</v>
-      </c>
-      <c r="D90" s="3">
-        <f t="shared" si="14"/>
-        <v>0.14270823301560323</v>
-      </c>
-      <c r="E90" s="14">
-        <f t="shared" si="15"/>
-        <v>7.4199297027598837E-2</v>
-      </c>
-      <c r="F90" s="4">
-        <f t="shared" si="16"/>
-        <v>7.4063576117031238E-2</v>
-      </c>
-      <c r="G90" s="4">
-        <f t="shared" si="17"/>
-        <v>1.7250152473215818E-2</v>
-      </c>
-      <c r="H90" s="4">
-        <v>15</v>
-      </c>
-      <c r="I90" s="4">
-        <f t="shared" si="18"/>
-        <v>75.999999999999972</v>
-      </c>
-      <c r="J90" s="4">
-        <f t="shared" si="19"/>
-        <v>4.4850396430361128</v>
-      </c>
-      <c r="K90" s="4">
-        <f t="shared" si="11"/>
-        <v>17.940158572144451</v>
-      </c>
-      <c r="L90" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M90" s="3">
-        <f>100*$B$12*K90/L90</f>
-        <v>5.980052857381484E-3</v>
+        <v>7.5000662927025303E-3</v>
       </c>
       <c r="N90" s="3">
-        <f t="shared" si="8"/>
-        <v>5.980052857381484E-3</v>
+        <f t="shared" si="9"/>
+        <v>7.5000662927025303E-3</v>
       </c>
     </row>
     <row r="91" spans="1:14">
       <c r="A91" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.1999999999999975</v>
       </c>
       <c r="B91" s="13">
+        <f t="shared" si="14"/>
+        <v>0.1923076923076924</v>
+      </c>
+      <c r="C91" s="4">
+        <f t="shared" si="15"/>
+        <v>0.1923076923076924</v>
+      </c>
+      <c r="D91" s="3">
+        <f t="shared" si="16"/>
+        <v>0.13765342435560171</v>
+      </c>
+      <c r="E91" s="14">
+        <f t="shared" si="17"/>
+        <v>7.1463086521907498E-2</v>
+      </c>
+      <c r="F91" s="4">
+        <f t="shared" si="18"/>
+        <v>7.1341804590863062E-2</v>
+      </c>
+      <c r="G91" s="4">
+        <f t="shared" si="19"/>
+        <v>1.6631311884726118E-2</v>
+      </c>
+      <c r="H91" s="4">
+        <v>15</v>
+      </c>
+      <c r="I91" s="4">
+        <f t="shared" si="20"/>
+        <v>77.499999999999972</v>
+      </c>
+      <c r="J91" s="4">
+        <f t="shared" si="21"/>
+        <v>4.1578279711815291</v>
+      </c>
+      <c r="K91" s="4">
         <f t="shared" si="12"/>
-        <v>0.1923076923076924</v>
-      </c>
-      <c r="C91" s="4">
+        <v>16.631311884726117</v>
+      </c>
+      <c r="L91" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M91" s="3">
         <f t="shared" si="13"/>
-        <v>0.1923076923076924</v>
-      </c>
-      <c r="D91" s="3">
-        <f t="shared" si="14"/>
-        <v>0.13765342435560171</v>
-      </c>
-      <c r="E91" s="14">
-        <f t="shared" si="15"/>
-        <v>7.1463086521907498E-2</v>
-      </c>
-      <c r="F91" s="4">
-        <f t="shared" si="16"/>
-        <v>7.1341804590863062E-2</v>
-      </c>
-      <c r="G91" s="4">
-        <f t="shared" si="17"/>
-        <v>1.6631311884726118E-2</v>
-      </c>
-      <c r="H91" s="4">
-        <v>15</v>
-      </c>
-      <c r="I91" s="4">
-        <f t="shared" si="18"/>
-        <v>77.499999999999972</v>
-      </c>
-      <c r="J91" s="4">
-        <f t="shared" si="19"/>
-        <v>4.3241410900287907</v>
-      </c>
-      <c r="K91" s="4">
-        <f t="shared" si="11"/>
-        <v>17.296564360115163</v>
-      </c>
-      <c r="L91" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M91" s="3">
-        <f>100*$B$12*K91/L91</f>
-        <v>5.7655214533717204E-3</v>
+        <v>7.2310051672722243E-3</v>
       </c>
       <c r="N91" s="3">
-        <f t="shared" si="8"/>
-        <v>5.7655214533717204E-3</v>
+        <f t="shared" si="9"/>
+        <v>7.2310051672722243E-3</v>
       </c>
     </row>
     <row r="92" spans="1:14">
       <c r="A92" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.2999999999999972</v>
       </c>
       <c r="B92" s="13">
+        <f t="shared" si="14"/>
+        <v>0.18867924528301896</v>
+      </c>
+      <c r="C92" s="4">
+        <f t="shared" si="15"/>
+        <v>0.18867924528301896</v>
+      </c>
+      <c r="D92" s="3">
+        <f t="shared" si="16"/>
+        <v>0.13285596119643034</v>
+      </c>
+      <c r="E92" s="14">
+        <f t="shared" si="17"/>
+        <v>6.8874293291192934E-2</v>
+      </c>
+      <c r="F92" s="4">
+        <f t="shared" si="18"/>
+        <v>6.8765696611956945E-2</v>
+      </c>
+      <c r="G92" s="4">
+        <f t="shared" si="19"/>
+        <v>1.6044541737293735E-2</v>
+      </c>
+      <c r="H92" s="4">
+        <v>15</v>
+      </c>
+      <c r="I92" s="4">
+        <f t="shared" si="20"/>
+        <v>78.999999999999972</v>
+      </c>
+      <c r="J92" s="4">
+        <f t="shared" si="21"/>
+        <v>4.0111354343234336</v>
+      </c>
+      <c r="K92" s="4">
         <f t="shared" si="12"/>
-        <v>0.18867924528301896</v>
-      </c>
-      <c r="C92" s="4">
+        <v>16.044541737293734</v>
+      </c>
+      <c r="L92" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M92" s="3">
         <f t="shared" si="13"/>
-        <v>0.18867924528301896</v>
-      </c>
-      <c r="D92" s="3">
-        <f t="shared" si="14"/>
-        <v>0.13285596119643034</v>
-      </c>
-      <c r="E92" s="14">
-        <f t="shared" si="15"/>
-        <v>6.8874293291192934E-2</v>
-      </c>
-      <c r="F92" s="4">
-        <f t="shared" si="16"/>
-        <v>6.8765696611956945E-2</v>
-      </c>
-      <c r="G92" s="4">
-        <f t="shared" si="17"/>
-        <v>1.6044541737293735E-2</v>
-      </c>
-      <c r="H92" s="4">
-        <v>15</v>
-      </c>
-      <c r="I92" s="4">
-        <f t="shared" si="18"/>
-        <v>78.999999999999972</v>
-      </c>
-      <c r="J92" s="4">
-        <f t="shared" si="19"/>
-        <v>4.1715808516963708</v>
-      </c>
-      <c r="K92" s="4">
-        <f t="shared" si="11"/>
-        <v>16.686323406785483</v>
-      </c>
-      <c r="L92" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M92" s="3">
-        <f>100*$B$12*K92/L92</f>
-        <v>5.5621078022618274E-3</v>
+        <v>6.9758877118668416E-3</v>
       </c>
       <c r="N92" s="3">
-        <f t="shared" si="8"/>
-        <v>5.5621078022618274E-3</v>
+        <f t="shared" si="9"/>
+        <v>6.9758877118668416E-3</v>
       </c>
     </row>
     <row r="93" spans="1:14">
       <c r="A93" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.3999999999999968</v>
       </c>
       <c r="B93" s="13">
+        <f t="shared" si="14"/>
+        <v>0.18518518518518529</v>
+      </c>
+      <c r="C93" s="4">
+        <f t="shared" si="15"/>
+        <v>0.18518518518518529</v>
+      </c>
+      <c r="D93" s="3">
+        <f t="shared" si="16"/>
+        <v>0.1282991235099504</v>
+      </c>
+      <c r="E93" s="14">
+        <f t="shared" si="17"/>
+        <v>6.64225803939823E-2</v>
+      </c>
+      <c r="F93" s="4">
+        <f t="shared" si="18"/>
+        <v>6.6325153598812137E-2</v>
+      </c>
+      <c r="G93" s="4">
+        <f t="shared" si="19"/>
+        <v>1.5487707873773186E-2</v>
+      </c>
+      <c r="H93" s="4">
+        <v>15</v>
+      </c>
+      <c r="I93" s="4">
+        <f t="shared" si="20"/>
+        <v>80.499999999999972</v>
+      </c>
+      <c r="J93" s="4">
+        <f t="shared" si="21"/>
+        <v>3.8719269684432964</v>
+      </c>
+      <c r="K93" s="4">
         <f t="shared" si="12"/>
-        <v>0.18518518518518529</v>
-      </c>
-      <c r="C93" s="4">
+        <v>15.487707873773186</v>
+      </c>
+      <c r="L93" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M93" s="3">
         <f t="shared" si="13"/>
-        <v>0.18518518518518529</v>
-      </c>
-      <c r="D93" s="3">
-        <f t="shared" si="14"/>
-        <v>0.1282991235099504</v>
-      </c>
-      <c r="E93" s="14">
-        <f t="shared" si="15"/>
-        <v>6.64225803939823E-2</v>
-      </c>
-      <c r="F93" s="4">
-        <f t="shared" si="16"/>
-        <v>6.6325153598812137E-2</v>
-      </c>
-      <c r="G93" s="4">
-        <f t="shared" si="17"/>
-        <v>1.5487707873773186E-2</v>
-      </c>
-      <c r="H93" s="4">
-        <v>15</v>
-      </c>
-      <c r="I93" s="4">
-        <f t="shared" si="18"/>
-        <v>80.499999999999972</v>
-      </c>
-      <c r="J93" s="4">
-        <f t="shared" si="19"/>
-        <v>4.0268040471810282</v>
-      </c>
-      <c r="K93" s="4">
-        <f t="shared" si="11"/>
-        <v>16.107216188724113</v>
-      </c>
-      <c r="L93" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M93" s="3">
-        <f>100*$B$12*K93/L93</f>
-        <v>5.3690720629080372E-3</v>
+        <v>6.7337860320752984E-3</v>
       </c>
       <c r="N93" s="3">
-        <f t="shared" si="8"/>
-        <v>5.3690720629080372E-3</v>
+        <f t="shared" si="9"/>
+        <v>6.7337860320752984E-3</v>
       </c>
     </row>
     <row r="94" spans="1:14">
       <c r="A94" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.4999999999999964</v>
       </c>
       <c r="B94" s="13">
+        <f t="shared" si="14"/>
+        <v>0.18181818181818193</v>
+      </c>
+      <c r="C94" s="4">
+        <f t="shared" si="15"/>
+        <v>0.18181818181818193</v>
+      </c>
+      <c r="D94" s="3">
+        <f t="shared" si="16"/>
+        <v>0.12396748761064799</v>
+      </c>
+      <c r="E94" s="14">
+        <f t="shared" si="17"/>
+        <v>6.4098497329625415E-2</v>
+      </c>
+      <c r="F94" s="4">
+        <f t="shared" si="18"/>
+        <v>6.4010927702901496E-2</v>
+      </c>
+      <c r="G94" s="4">
+        <f t="shared" si="19"/>
+        <v>1.4958846995866318E-2</v>
+      </c>
+      <c r="H94" s="4">
+        <v>15</v>
+      </c>
+      <c r="I94" s="4">
+        <f t="shared" si="20"/>
+        <v>81.999999999999972</v>
+      </c>
+      <c r="J94" s="4">
+        <f t="shared" si="21"/>
+        <v>3.7397117489665797</v>
+      </c>
+      <c r="K94" s="4">
         <f t="shared" si="12"/>
-        <v>0.18181818181818193</v>
-      </c>
-      <c r="C94" s="4">
+        <v>14.958846995866319</v>
+      </c>
+      <c r="L94" s="4">
+        <v>23000</v>
+      </c>
+      <c r="M94" s="3">
         <f t="shared" si="13"/>
-        <v>0.18181818181818193</v>
-      </c>
-      <c r="D94" s="3">
-        <f t="shared" si="14"/>
-        <v>0.12396748761064799</v>
-      </c>
-      <c r="E94" s="14">
-        <f t="shared" si="15"/>
-        <v>6.4098497329625415E-2</v>
-      </c>
-      <c r="F94" s="4">
-        <f t="shared" si="16"/>
-        <v>6.4010927702901496E-2</v>
-      </c>
-      <c r="G94" s="4">
-        <f t="shared" si="17"/>
-        <v>1.4958846995866318E-2</v>
-      </c>
-      <c r="H94" s="4">
-        <v>15</v>
-      </c>
-      <c r="I94" s="4">
-        <f t="shared" si="18"/>
-        <v>81.999999999999972</v>
-      </c>
-      <c r="J94" s="4">
-        <f t="shared" si="19"/>
-        <v>3.8893002189252428</v>
-      </c>
-      <c r="K94" s="4">
-        <f t="shared" si="11"/>
-        <v>15.557200875700971</v>
-      </c>
-      <c r="L94" s="4">
-        <v>30000</v>
-      </c>
-      <c r="M94" s="3">
-        <f>100*$B$12*K94/L94</f>
-        <v>5.185733625233657E-3</v>
+        <v>6.5038465199418775E-3</v>
       </c>
       <c r="N94" s="3">
-        <f t="shared" si="8"/>
-        <v>5.185733625233657E-3</v>
+        <f t="shared" si="9"/>
+        <v>6.5038465199418775E-3</v>
       </c>
     </row>
     <row r="95" spans="1:14">
       <c r="A95" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.5999999999999961</v>
       </c>
       <c r="B95" s="13">
-        <f t="shared" ref="B95:B104" si="20">$B$10/A95</f>
+        <f t="shared" ref="B95:B104" si="22">$B$10/A95</f>
         <v>0.17857142857142869</v>
       </c>
       <c r="C95" s="4">
-        <f t="shared" ref="C95:C104" si="21">$B$9/A95</f>
+        <f t="shared" ref="C95:C104" si="23">$B$9/A95</f>
         <v>0.17857142857142869</v>
       </c>
       <c r="D95" s="3">
-        <f t="shared" ref="D95:D104" si="22">2*C95*B95*SQRT(B95^2+C95^2+1)*(B95^2+C95^2+2)/((C95^2+B95^2+B95^2*C95^2+1)*(C95^2+B95^2+1))</f>
+        <f t="shared" ref="D95:D104" si="24">2*C95*B95*SQRT(B95^2+C95^2+1)*(B95^2+C95^2+2)/((C95^2+B95^2+B95^2*C95^2+1)*(C95^2+B95^2+1))</f>
         <v>0.11984681155626975</v>
       </c>
       <c r="E95" s="14">
-        <f t="shared" ref="E95:E104" si="23">((2*B95*C95*SQRT(B95^2+C95^2+1)/(B95^2+C95^2-C95^2 *B95^2+1)))</f>
+        <f t="shared" ref="E95:E104" si="25">((2*B95*C95*SQRT(B95^2+C95^2+1)/(B95^2+C95^2-C95^2 *B95^2+1)))</f>
         <v>6.1893390575374213E-2</v>
       </c>
       <c r="F95" s="4">
-        <f t="shared" ref="F95:F104" si="24">IF(E95&lt;0,ATAN(E95)+PI(),ATAN(E95))</f>
+        <f t="shared" ref="F95:F104" si="26">IF(E95&lt;0,ATAN(E95)+PI(),ATAN(E95))</f>
         <v>6.1814538172165145E-2</v>
       </c>
       <c r="G95" s="4">
-        <f t="shared" ref="G95:G104" si="25">(D95+F95)/(4*PI())</f>
+        <f t="shared" ref="G95:G104" si="27">(D95+F95)/(4*PI())</f>
         <v>1.4456150889012977E-2</v>
       </c>
       <c r="H95" s="4">
         <v>15</v>
       </c>
       <c r="I95" s="4">
-        <f t="shared" ref="I95:I104" si="26">I94+(A95-A94)*H95</f>
+        <f t="shared" ref="I95:I104" si="28">I94+(A95-A94)*H95</f>
         <v>83.499999999999972</v>
       </c>
       <c r="J95" s="4">
-        <f t="shared" ref="J95:J104" si="27">G95*$B$14</f>
-        <v>3.758599231143374</v>
+        <f t="shared" ref="J95:J104" si="29">G95*$B$14</f>
+        <v>3.614037722253244</v>
       </c>
       <c r="K95" s="4">
-        <f t="shared" si="11"/>
-        <v>15.034396924573496</v>
+        <f t="shared" si="12"/>
+        <v>14.456150889012976</v>
       </c>
       <c r="L95" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M95" s="3">
-        <f>100*$B$12*K95/L95</f>
-        <v>5.011465641524499E-3</v>
+        <f t="shared" si="13"/>
+        <v>6.2852829952230339E-3</v>
       </c>
       <c r="N95" s="3">
-        <f t="shared" si="8"/>
-        <v>5.011465641524499E-3</v>
+        <f t="shared" si="9"/>
+        <v>6.2852829952230339E-3</v>
       </c>
     </row>
     <row r="96" spans="1:14">
       <c r="A96" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.6999999999999957</v>
       </c>
       <c r="B96" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.1754385964912282</v>
       </c>
       <c r="C96" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.1754385964912282</v>
       </c>
       <c r="D96" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.11592393168469822</v>
       </c>
       <c r="E96" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>5.9799324480417936E-2</v>
       </c>
       <c r="F96" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>5.9728197045770502E-2</v>
       </c>
       <c r="G96" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.3977952276034013E-2</v>
       </c>
       <c r="H96" s="4">
         <v>15</v>
       </c>
       <c r="I96" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>84.999999999999972</v>
       </c>
       <c r="J96" s="4">
-        <f t="shared" si="27"/>
-        <v>3.6342675917688436</v>
+        <f t="shared" si="29"/>
+        <v>3.4944880690085034</v>
       </c>
       <c r="K96" s="4">
-        <f t="shared" si="11"/>
-        <v>14.537070367075374</v>
+        <f t="shared" si="12"/>
+        <v>13.977952276034014</v>
       </c>
       <c r="L96" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M96" s="3">
-        <f>100*$B$12*K96/L96</f>
-        <v>4.8456901223584582E-3</v>
+        <f t="shared" si="13"/>
+        <v>6.0773705547973976E-3</v>
       </c>
       <c r="N96" s="3">
-        <f t="shared" si="8"/>
-        <v>4.8456901223584582E-3</v>
+        <f t="shared" si="9"/>
+        <v>6.0773705547973976E-3</v>
       </c>
     </row>
     <row r="97" spans="1:14">
       <c r="A97" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.7999999999999954</v>
       </c>
       <c r="B97" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.17241379310344843</v>
       </c>
       <c r="C97" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.17241379310344843</v>
       </c>
       <c r="D97" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.11218666913978907</v>
       </c>
       <c r="E97" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>5.7809011166115996E-2</v>
       </c>
       <c r="F97" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>5.7744743022679908E-2</v>
       </c>
       <c r="G97" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.3522712116121582E-2</v>
       </c>
       <c r="H97" s="4">
         <v>15</v>
       </c>
       <c r="I97" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>86.499999999999972</v>
       </c>
       <c r="J97" s="4">
-        <f t="shared" si="27"/>
-        <v>3.5159051501916112</v>
+        <f t="shared" si="29"/>
+        <v>3.3806780290303955</v>
       </c>
       <c r="K97" s="4">
-        <f t="shared" si="11"/>
-        <v>14.063620600766445</v>
+        <f t="shared" si="12"/>
+        <v>13.522712116121582</v>
       </c>
       <c r="L97" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M97" s="3">
-        <f>100*$B$12*K97/L97</f>
-        <v>4.687873533588815E-3</v>
+        <f t="shared" si="13"/>
+        <v>5.8794400504876441E-3</v>
       </c>
       <c r="N97" s="3">
-        <f t="shared" si="8"/>
-        <v>4.687873533588815E-3</v>
+        <f t="shared" si="9"/>
+        <v>5.8794400504876441E-3</v>
       </c>
     </row>
     <row r="98" spans="1:14">
       <c r="A98" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.899999999999995</v>
       </c>
       <c r="B98" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.16949152542372894</v>
       </c>
       <c r="C98" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.16949152542372894</v>
       </c>
       <c r="D98" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.10862374535833498</v>
       </c>
       <c r="E98" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>5.5915748277525892E-2</v>
       </c>
       <c r="F98" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>5.5857582503674945E-2</v>
       </c>
       <c r="G98" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.3089008187778785E-2</v>
       </c>
       <c r="H98" s="4">
         <v>15</v>
       </c>
       <c r="I98" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>87.999999999999972</v>
       </c>
       <c r="J98" s="4">
-        <f t="shared" si="27"/>
-        <v>3.4031421288224841</v>
+        <f t="shared" si="29"/>
+        <v>3.2722520469446961</v>
       </c>
       <c r="K98" s="4">
-        <f t="shared" si="11"/>
-        <v>13.612568515289936</v>
+        <f t="shared" si="12"/>
+        <v>13.089008187778784</v>
       </c>
       <c r="L98" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M98" s="3">
-        <f>100*$B$12*K98/L98</f>
-        <v>4.5375228384299787E-3</v>
+        <f t="shared" si="13"/>
+        <v>5.6908731251212111E-3</v>
       </c>
       <c r="N98" s="3">
-        <f t="shared" si="8"/>
-        <v>4.5375228384299787E-3</v>
+        <f t="shared" si="9"/>
+        <v>5.6908731251212111E-3</v>
       </c>
     </row>
     <row r="99" spans="1:14">
       <c r="A99" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>5.9999999999999947</v>
       </c>
       <c r="B99" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.16666666666666682</v>
       </c>
       <c r="C99" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.16666666666666682</v>
       </c>
       <c r="D99" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.10522470559833266</v>
       </c>
       <c r="E99" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>5.4113363595923822E-2</v>
       </c>
       <c r="F99" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>5.4060636940556954E-2</v>
       </c>
       <c r="G99" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.2675524813575017E-2</v>
       </c>
       <c r="H99" s="4">
         <v>15</v>
       </c>
       <c r="I99" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>89.499999999999972</v>
       </c>
       <c r="J99" s="4">
-        <f t="shared" si="27"/>
-        <v>3.2956364515295045</v>
+        <f t="shared" si="29"/>
+        <v>3.1688812033937541</v>
       </c>
       <c r="K99" s="4">
-        <f t="shared" si="11"/>
-        <v>13.182545806118018</v>
+        <f t="shared" si="12"/>
+        <v>12.675524813575016</v>
       </c>
       <c r="L99" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M99" s="3">
-        <f>100*$B$12*K99/L99</f>
-        <v>4.3941819353726722E-3</v>
+        <f t="shared" si="13"/>
+        <v>5.5110977450326159E-3</v>
       </c>
       <c r="N99" s="3">
-        <f t="shared" si="8"/>
-        <v>4.3941819353726722E-3</v>
+        <f t="shared" si="9"/>
+        <v>5.5110977450326159E-3</v>
       </c>
     </row>
     <row r="100" spans="1:14">
       <c r="A100" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.0999999999999943</v>
       </c>
       <c r="B100" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.16393442622950835</v>
       </c>
       <c r="C100" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.16393442622950835</v>
       </c>
       <c r="D100" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>0.10197984968601227</v>
       </c>
       <c r="E100" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>5.239616566080444E-2</v>
       </c>
       <c r="F100" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>5.2348295740882629E-2</v>
       </c>
       <c r="G100" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.2281043601447604E-2</v>
       </c>
       <c r="H100" s="4">
         <v>15</v>
       </c>
       <c r="I100" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>90.999999999999972</v>
       </c>
       <c r="J100" s="4">
-        <f t="shared" si="27"/>
-        <v>3.1930713363763767</v>
+        <f t="shared" si="29"/>
+        <v>3.0702609003619008</v>
       </c>
       <c r="K100" s="4">
-        <f t="shared" si="11"/>
-        <v>12.772285345505507</v>
+        <f t="shared" si="12"/>
+        <v>12.281043601447603</v>
       </c>
       <c r="L100" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M100" s="3">
-        <f>100*$B$12*K100/L100</f>
-        <v>4.2574284485018361E-3</v>
+        <f t="shared" si="13"/>
+        <v>5.3395841745424366E-3</v>
       </c>
       <c r="N100" s="3">
-        <f t="shared" si="8"/>
-        <v>4.2574284485018361E-3</v>
+        <f t="shared" si="9"/>
+        <v>5.3395841745424366E-3</v>
       </c>
     </row>
     <row r="101" spans="1:14">
       <c r="A101" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.199999999999994</v>
       </c>
       <c r="B101" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.16129032258064532</v>
       </c>
       <c r="C101" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.16129032258064532</v>
       </c>
       <c r="D101" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>9.8880169246428215E-2</v>
       </c>
       <c r="E101" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>5.0758899667244617E-2</v>
       </c>
       <c r="F101" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>5.0715374074820234E-2</v>
       </c>
       <c r="G101" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.1904435092047231E-2</v>
       </c>
       <c r="H101" s="4">
         <v>15</v>
       </c>
       <c r="I101" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>92.499999999999972</v>
       </c>
       <c r="J101" s="4">
-        <f t="shared" si="27"/>
-        <v>3.0951531239322798</v>
+        <f t="shared" si="29"/>
+        <v>2.9761087730118079</v>
       </c>
       <c r="K101" s="4">
-        <f t="shared" si="11"/>
-        <v>12.380612495729119</v>
+        <f t="shared" si="12"/>
+        <v>11.904435092047231</v>
       </c>
       <c r="L101" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M101" s="3">
-        <f>100*$B$12*K101/L101</f>
-        <v>4.1268708319097064E-3</v>
+        <f t="shared" si="13"/>
+        <v>5.1758413443683616E-3</v>
       </c>
       <c r="N101" s="3">
-        <f t="shared" si="8"/>
-        <v>4.1268708319097064E-3</v>
+        <f t="shared" si="9"/>
+        <v>5.1758413443683616E-3</v>
       </c>
     </row>
     <row r="102" spans="1:14">
       <c r="A102" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.2999999999999936</v>
       </c>
       <c r="B102" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.15873015873015889</v>
       </c>
       <c r="C102" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.15873015873015889</v>
       </c>
       <c r="D102" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>9.5917290760625426E-2</v>
       </c>
       <c r="E102" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>4.9196708004115269E-2</v>
       </c>
       <c r="F102" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>4.9157075015035051E-2</v>
       </c>
       <c r="G102" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.1544651214559025E-2</v>
       </c>
       <c r="H102" s="4">
         <v>15</v>
       </c>
       <c r="I102" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>93.999999999999972</v>
       </c>
       <c r="J102" s="4">
-        <f t="shared" si="27"/>
-        <v>3.0016093157853465</v>
+        <f t="shared" si="29"/>
+        <v>2.8861628036397562</v>
       </c>
       <c r="K102" s="4">
-        <f t="shared" si="11"/>
-        <v>12.006437263141386</v>
+        <f t="shared" si="12"/>
+        <v>11.544651214559025</v>
       </c>
       <c r="L102" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M102" s="3">
-        <f>100*$B$12*K102/L102</f>
-        <v>4.0021457543804621E-3</v>
+        <f t="shared" si="13"/>
+        <v>5.0194135715474018E-3</v>
       </c>
       <c r="N102" s="3">
-        <f t="shared" si="8"/>
-        <v>4.0021457543804621E-3</v>
+        <f t="shared" si="9"/>
+        <v>5.0194135715474018E-3</v>
       </c>
     </row>
     <row r="103" spans="1:14">
       <c r="A103" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.3999999999999932</v>
       </c>
       <c r="B103" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.15625000000000017</v>
       </c>
       <c r="C103" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.15625000000000017</v>
       </c>
       <c r="D103" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>9.3083423862322934E-2</v>
       </c>
       <c r="E103" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>4.7705094883375189E-2</v>
       </c>
       <c r="F103" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>4.7668955513048727E-2</v>
       </c>
       <c r="G103" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.120071846476807E-2</v>
       </c>
       <c r="H103" s="4">
         <v>15</v>
       </c>
       <c r="I103" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>95.499999999999972</v>
       </c>
       <c r="J103" s="4">
-        <f t="shared" si="27"/>
-        <v>2.9121868008396983</v>
+        <f t="shared" si="29"/>
+        <v>2.8001796161920174</v>
       </c>
       <c r="K103" s="4">
-        <f t="shared" si="11"/>
-        <v>11.648747203358793</v>
+        <f t="shared" si="12"/>
+        <v>11.20071846476807</v>
       </c>
       <c r="L103" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M103" s="3">
-        <f>100*$B$12*K103/L103</f>
-        <v>3.882915734452931E-3</v>
+        <f t="shared" si="13"/>
+        <v>4.8698775933774217E-3</v>
       </c>
       <c r="N103" s="3">
-        <f t="shared" si="8"/>
-        <v>3.882915734452931E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.8698775933774217E-3</v>
       </c>
     </row>
     <row r="104" spans="1:14">
       <c r="A104" s="21">
-        <f t="shared" si="9"/>
+        <f t="shared" si="10"/>
         <v>6.4999999999999929</v>
       </c>
       <c r="B104" s="13">
-        <f t="shared" si="20"/>
+        <f t="shared" si="22"/>
         <v>0.15384615384615402</v>
       </c>
       <c r="C104" s="4">
-        <f t="shared" si="21"/>
+        <f t="shared" si="23"/>
         <v>0.15384615384615402</v>
       </c>
       <c r="D104" s="3">
-        <f t="shared" si="22"/>
+        <f t="shared" si="24"/>
         <v>9.0371314349473264E-2</v>
       </c>
       <c r="E104" s="14">
-        <f t="shared" si="23"/>
+        <f t="shared" si="25"/>
         <v>4.6279894582988604E-2</v>
       </c>
       <c r="F104" s="4">
-        <f t="shared" si="24"/>
+        <f t="shared" si="26"/>
         <v>4.6246895778026036E-2</v>
       </c>
       <c r="G104" s="4">
-        <f t="shared" si="25"/>
+        <f t="shared" si="27"/>
         <v>1.0871731729079376E-2</v>
       </c>
       <c r="H104" s="4">
         <v>15</v>
       </c>
       <c r="I104" s="4">
-        <f t="shared" si="26"/>
+        <f t="shared" si="28"/>
         <v>96.999999999999972</v>
       </c>
       <c r="J104" s="4">
-        <f t="shared" si="27"/>
-        <v>2.8266502495606378</v>
+        <f t="shared" si="29"/>
+        <v>2.7179329322698438</v>
       </c>
       <c r="K104" s="4">
-        <f t="shared" ref="K104" si="28">4*J104</f>
-        <v>11.306600998242551</v>
+        <f t="shared" ref="K104" si="30">4*J104</f>
+        <v>10.871731729079375</v>
       </c>
       <c r="L104" s="4">
-        <v>30000</v>
+        <v>23000</v>
       </c>
       <c r="M104" s="3">
-        <f>100*$B$12*K104/L104</f>
-        <v>3.7688669994141838E-3</v>
+        <f t="shared" ref="M104:M135" si="31">100*$B$12*K104/L104</f>
+        <v>4.7268398822084235E-3</v>
       </c>
       <c r="N104" s="3">
-        <f t="shared" si="8"/>
-        <v>3.7688669994141838E-3</v>
+        <f t="shared" si="9"/>
+        <v>4.7268398822084235E-3</v>
       </c>
     </row>
     <row r="105" spans="1:14">
